--- a/flight_data/live_flights.xlsx
+++ b/flight_data/live_flights.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -512,6 +512,6736 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>WY102</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0700</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>OV514</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0730</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0705</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>OV902</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Beringin</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Beringin</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0730</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>OV438</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Colombo</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Colombo</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0735</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0715</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>OV796</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Jaipur</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Jaipur</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0845</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0736</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FZ045</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>flydubai</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0810</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>G9112</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Air Arabia</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0910</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>WY672</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0950</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>WY252</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1035</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Bags on Belt</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>WY226</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EY692</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Etihad Airways</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Arrived</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>WY242</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1045</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>WY212</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1050</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>On Time</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>WY266</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1055</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Bags on Belt</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>6X7219</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>6X</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Shiraz</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Shiraz</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1125</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>OV134</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Duqm</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Duqm</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>On Time</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>WY818</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1150</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>On Time</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>OV402</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1120</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>WY844</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Manila</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Manila</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>OV242</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1210</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>OV102</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>On Time</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>WY822</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>WY604</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>OV5024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1225</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>WY904</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>On Time</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>6X1129</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>6X</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Tehran</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Tehran</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1245</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>OV5022</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Fahud</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Fahud</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>WY834</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>On Time</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PF734</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Rawalpindi</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Rawalpindi</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1310</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>On Time</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PF736</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Sialkot</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Sialkot</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1425</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>OV288</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>WY892</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>WY824</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>WY832</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>0015</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>WY682</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>0015</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>WY662</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>0015</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>OV316</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Al Jiza</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Al Jiza</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>0050</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>0013</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BS321</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>0100</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>0021</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TK774</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Turkish Airlines</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>0030</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>0107</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>6E1273</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>0150</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>IX441</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>0150</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>6E1271</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>0200</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>0143</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>OV404</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>0215</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>0114</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>EK866</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Emirates</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>0330</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ET624</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ethiopian Airlines</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>0335</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>QR1148</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Qatar Airways</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0355</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>PC830</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Pegasus Airlines</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Pendik, Istanbul</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Pendik, Istanbul</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0330</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0421</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>OV498</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0535</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0459</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>WY678</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0510</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>WY674</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0525</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>WY154</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0525</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>OV564</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Rawalpindi</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Rawalpindi</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>0545</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>0520</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>WY148</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Rome</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Rome</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>0545</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>OV774</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>0605</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>OV736</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>0605</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>0537</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>WY144</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Ferno</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Ferno</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>0605</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>OV598</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Peshawar</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Peshawar</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>0620</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>0604</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>WY132</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>0620</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>OV506</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Sialkot</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Sialkot</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>0635</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>0611</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>OV762</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>0650</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>0628</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>OV784</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>0640</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>OV706</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>0715</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>0628</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>OV287</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>0715</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>OV5023</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>0810</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>OV5021</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Fahud</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Fahud</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>0820</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>WY317</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>0825</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>WY223</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>0825</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>OV133</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Duqm</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Duqm</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>0830</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>OV101</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>0830</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>OV811</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Vienna</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Vienna</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>0835</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>WY815</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>0840</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>WY603</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>0840</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>OV283</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>0840</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>WY903</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>0845</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>WY823</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>0845</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>OV241</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>0850</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>0907</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>WY2801</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>0900</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>FZ046</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>flydubai</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>0910</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>WY843</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Manila</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Manila</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>0915</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>WY203</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>0920</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>OV335</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Baghdad</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Baghdad</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>0940</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>OV271</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>0940</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>G9113</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Air Arabia</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>OV365</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>WY831</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Boarding</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>WY245</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Gate Open</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>OV927</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Almaty</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Almaty</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>EY693</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Etihad Airways</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>6X7220</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>6X</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Shiraz</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Shiraz</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Delayed</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>OV103</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>WY905</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>OV205</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>WY413</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Amman</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Amman</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>WY117</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>1320</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>OV5025</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>1330</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>OV285</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>WY683</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>1355</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>WY123</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>1355</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>PF735</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Rawalpindi</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Rawalpindi</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>WY101</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>1415</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>6X1128</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>6X</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Tehran</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Tehran</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>1415</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>OV227</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Kuwait City</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Kuwait City</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>OV391</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Port Sudan</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Port Sudan</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>WY609</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>WY663</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>1435</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>WY405</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>1440</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>WY655</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Manama</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Manama</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>1445</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>WY675</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>1450</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>OV597</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Peshawar</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Peshawar</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>IX236</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>0015</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>OV761</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>0025</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>OV401</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>0115</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>OV795</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Jaipur</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Jaipur</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>0150</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>WY849</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>0150</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>BS322</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>0200</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>WY251</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>0205</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>TK775</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Turkish Airlines</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>0130</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>0222</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Delayed</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>WY671</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>WY225</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>WY211</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>6E1274</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>WY265</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>0300</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>6E1272</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>0300</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>IX442</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>0307</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>OV513</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>0315</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>WY241</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>0320</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>ET625</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Ethiopian Airlines</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>0425</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>EK867</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Emirates</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>0440</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>PC831</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Pegasus Airlines</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Pendik, Istanbul</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Pendik, Istanbul</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>0445</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>0537</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>QR1149</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>14SEP</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Qatar Airways</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>0530</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>0612</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:03</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/flight_data/live_flights.xlsx
+++ b/flight_data/live_flights.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -512,6 +512,5794 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>WY892</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>WY662</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0015</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TK774</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Turkish Airlines</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0030</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>WY682</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0035</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>WY916</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0045</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PK171</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PIA Pakistan International Airlines</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Multan</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Multan</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0115</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>OV772</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0135</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0114</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>6E1273</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0150</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>IX441</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0150</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>6E1271</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0200</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0140</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>OV404</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0215</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0106</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>WY2802</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Luanda</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Luanda</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0135</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Arrived</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EK866</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Emirates</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0330</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0314</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ET624</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ethiopian Airlines</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0335</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>QR1148</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Qatar Airways</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0355</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Bags on Belt</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TC408</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>TC</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Dar es Salaam</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Dar es Salaam</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0220</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0426</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>WY412</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Amman</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Amman</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0405</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>WY118</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0405</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Arrived</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>WY124</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0445</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>On Time</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>WY674</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0510</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>WY172</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0515</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>OV522</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Lahore</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Lahore</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0540</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0508</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>OV564</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Rawalpindi</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Rawalpindi</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>0545</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0522</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>OV538</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Multan</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Multan</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0545</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0513</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>OV774</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0605</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0544</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>OV736</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>0605</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0541</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>WY678</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>0510</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0610</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>OV506</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Sialkot</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Sialkot</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>0635</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>On Time</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>OV762</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>0650</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>OV706</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>0715</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>0658</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>WY102</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>0700</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>On Time</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>WY686</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>OV514</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>0730</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>OV438</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Colombo</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Colombo</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>0735</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>0705</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>WY184</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>0740</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>WY408</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>FZ045</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>flydubai</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>0810</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>OV498</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>0835</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>On Time</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>G9112</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Air Arabia</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>0910</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>WY672</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>0950</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>6X7219</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>6X</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Shiraz</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Shiraz</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>I36637</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>I3</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Shiraz</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Shiraz</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>OV134</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Duqm</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Duqm</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>WY252</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1035</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>EY692</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Etihad Airways</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>WY242</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1045</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>WY266</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1055</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>WY202</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>WY818</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1150</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>OV402</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>WY844</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Manila</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Manila</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>WY822</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>OV102</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>WY604</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>BG721</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Biman Bangladesh Airlines</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>1220</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>OV5014</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1225</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>WY707</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Zanzibar</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Zanzibar</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>1225</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>WY904</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>OV5012</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Fahud</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Fahud</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>WY832</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>0025</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2314</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>OV316</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Al Jiza</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Al Jiza</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>0035</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2357</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>IX236</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>0015</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>OV761</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>0025</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>0051</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>OV401</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>0115</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>TK775</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Turkish Airlines</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>0130</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>WY103</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>0135</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>WY685</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>0145</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>WY849</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>0150</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>0235</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>WY251</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>0205</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>WY671</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>PK172</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>PIA Pakistan International Airlines</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Multan</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Multan</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>0230</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>6E1274</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>IX442</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>WY265</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>0300</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>6E1272</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>0300</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>OV513</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>0315</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>WY241</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>0320</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>ET625</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ethiopian Airlines</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>0425</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Gate Closed</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>EK867</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Emirates</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>0440</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Gate Closed</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>TC409</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>TC</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Zanzibar</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Zanzibar</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>0350</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>0520</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Gate Open</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>WY201</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>0505</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Gate Open</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>QR1149</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Qatar Airways</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>0530</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>OV391</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Port Sudan</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Port Sudan</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>0705</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>OV133</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Duqm</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Duqm</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>WY891</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>0800</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>OV5013</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>0810</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>OV5011</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Fahud</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Fahud</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>0820</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>WY223</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>0825</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>OV101</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>0830</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>OV283</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>0840</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>WY815</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>0840</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>WY603</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>0840</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>WY903</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>0845</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>WY823</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>0845</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>FZ046</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>flydubai</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>0910</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>WY253</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>0920</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>WY203</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>0920</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>OV335</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Baghdad</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Baghdad</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>0940</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>OV271</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>0940</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>G9113</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Air Arabia</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>OV341</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Mogadishu</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Mogadishu</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>OV365</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>WY245</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>WY831</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>6X7220</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>6X</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Shiraz</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Shiraz</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>I36638</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>I3</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Shiraz</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Shiraz</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>OV5093</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Mukhaizna Oil Field</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Mukhaizna Oil Field</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>WY917</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>EY693</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Etihad Airways</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>OV103</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>OV205</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>WY165</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:41</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/flight_data/live_flights.xlsx
+++ b/flight_data/live_flights.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M126"/>
+  <dimension ref="A1:M149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -515,7 +515,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6X6810</t>
+          <t>WY908</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,22 +525,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6X</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Tehran</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Tehran</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>1715</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -554,19 +554,19 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>OV5094</t>
+          <t>WY254</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -576,29 +576,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mukhaizna Oil Field</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mukhaizna Oil Field</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1445</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1424</t>
-        </is>
-      </c>
+          <t>1750</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Bags Delivered</t>
@@ -609,19 +605,19 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6X7312</t>
+          <t>WY246</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,28 +627,28 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6X</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mashhad</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mashhad</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1750</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -660,12 +656,12 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -715,12 +711,12 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -770,12 +766,12 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -821,12 +817,12 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -872,12 +868,12 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -923,12 +919,12 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -974,12 +970,12 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1021,12 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1072,12 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -1131,12 +1127,12 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1178,12 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1229,12 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1284,12 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1339,12 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1390,12 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -1449,12 +1445,12 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -1500,12 +1496,12 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -1551,12 +1547,12 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -1606,12 +1602,12 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -1657,12 +1653,12 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -1708,12 +1704,12 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1755,12 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -1810,12 +1806,12 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -1861,12 +1857,12 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -1916,12 +1912,12 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -1971,12 +1967,12 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -2026,12 +2022,12 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -2081,12 +2077,12 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -2136,12 +2132,12 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -2191,12 +2187,12 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -2242,12 +2238,12 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -2293,12 +2289,12 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -2348,12 +2344,12 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -2399,12 +2395,12 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -2450,12 +2446,12 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -2505,12 +2501,12 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2556,12 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -2611,12 +2607,12 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -2662,12 +2658,12 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -2713,12 +2709,12 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -2764,12 +2760,12 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -2815,12 +2811,12 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -2866,12 +2862,12 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -2917,12 +2913,12 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -2968,12 +2964,12 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -3019,12 +3015,12 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -3070,12 +3066,12 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3121,12 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -3176,12 +3172,12 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3227,12 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -3286,12 +3282,12 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -3337,12 +3333,12 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -3388,12 +3384,12 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -3443,12 +3439,12 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -3494,12 +3490,12 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -3549,12 +3545,12 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -3600,12 +3596,12 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -3651,12 +3647,12 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -3702,12 +3698,12 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
@@ -3757,19 +3753,19 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>WY171</t>
+          <t>6X6810</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3779,28 +3775,28 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>6X</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>Tehran</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>Tehran</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Departed</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -3808,19 +3804,19 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>WY131</t>
+          <t>OV5094</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3830,28 +3826,32 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Mukhaizna Oil Field</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Mukhaizna Oil Field</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1410</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr"/>
+          <t>1445</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>1424</t>
+        </is>
+      </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Departed</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -3859,19 +3859,19 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BG222</t>
+          <t>OV392</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3881,32 +3881,32 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Biman Bangladesh Airlines</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Port Sudan</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Port Sudan</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>1425</t>
+          <t>1437</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Departed</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -3914,19 +3914,19 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>WY101</t>
+          <t>6X7312</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3936,28 +3936,28 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>6X</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LHR</t>
+          <t>Mashhad</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Mashhad</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Departed</t>
+          <t>Cancelled</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -3965,19 +3965,19 @@
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>OV227</t>
+          <t>WY204</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3987,28 +3987,28 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Kuwait City</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Kuwait City</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>1545</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Departed</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -4016,19 +4016,19 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>WY663</t>
+          <t>OV104</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4038,28 +4038,28 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>DOH</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Doha</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Departed</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -4067,19 +4067,19 @@
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>WY405</t>
+          <t>OV284</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4089,28 +4089,28 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Cairo</t>
+          <t>JED</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Cairo</t>
+          <t>Jeddah</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>1620</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Departed</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -4118,19 +4118,19 @@
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>WY655</t>
+          <t>WY224</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4145,23 +4145,23 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Manama</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Manama</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Departed</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -4169,19 +4169,19 @@
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>WY675</t>
+          <t>OV5016</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4191,28 +4191,28 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>JED</t>
+          <t>Marmul</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Jeddah</t>
+          <t>Marmul</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1645</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Departed</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -4220,19 +4220,19 @@
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>IX236</t>
+          <t>OV272</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4242,28 +4242,28 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Medina</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Medina</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>0015</t>
+          <t>1645</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Departed</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -4271,19 +4271,19 @@
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>OV761</t>
+          <t>OV336</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4298,27 +4298,27 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Baghdad</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Baghdad</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>0025</t>
+          <t>1715</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>0051</t>
+          <t>1646</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Departed</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -4326,19 +4326,19 @@
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>OV401</t>
+          <t>OV105</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4353,17 +4353,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Chattogram</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Chattogram</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>0115</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -4377,19 +4377,19 @@
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>TK775</t>
+          <t>OV245</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4399,22 +4399,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Turkish Airlines</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Sharjah</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Sharjah</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>0130</t>
+          <t>1720</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
@@ -4428,19 +4428,19 @@
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>WY103</t>
+          <t>WY623</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4455,17 +4455,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LHR</t>
+          <t>DXB</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>0135</t>
+          <t>1745</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -4479,19 +4479,19 @@
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>WY685</t>
+          <t>OV901</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4501,25 +4501,29 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Riyadh</t>
+          <t>Beringin</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Riyadh</t>
+          <t>Beringin</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>0145</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr"/>
+          <t>1745</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>1813</t>
+        </is>
+      </c>
       <c r="H78" t="inlineStr">
         <is>
           <t>Departed</t>
@@ -4530,19 +4534,19 @@
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>WY251</t>
+          <t>IX236</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4552,22 +4556,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>0205</t>
+          <t>0015</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
@@ -4581,19 +4585,19 @@
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>WY671</t>
+          <t>OV761</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4603,25 +4607,29 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>JED</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Jeddah</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>0225</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr"/>
+          <t>0025</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>0051</t>
+        </is>
+      </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>Departed</t>
@@ -4632,19 +4640,19 @@
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>PK172</t>
+          <t>OV401</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4654,22 +4662,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>PIA Pakistan International Airlines</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Multan</t>
+          <t>Chattogram</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Multan</t>
+          <t>Chattogram</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>0230</t>
+          <t>0115</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
@@ -4683,19 +4691,19 @@
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>6E1274</t>
+          <t>TK775</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4705,22 +4713,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>6E</t>
+          <t>Turkish Airlines</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>0250</t>
+          <t>0130</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -4734,19 +4742,19 @@
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>IX442</t>
+          <t>WY103</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4756,22 +4764,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>LHR</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>London</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>0250</t>
+          <t>0135</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
@@ -4785,19 +4793,19 @@
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>WY265</t>
+          <t>WY685</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4812,17 +4820,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Lucknow</t>
+          <t>Riyadh</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Lucknow</t>
+          <t>Riyadh</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>0300</t>
+          <t>0145</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
@@ -4836,19 +4844,19 @@
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>6E1272</t>
+          <t>WY251</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4858,22 +4866,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>6E</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>0300</t>
+          <t>0205</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
@@ -4887,19 +4895,19 @@
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>OV513</t>
+          <t>WY671</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4909,22 +4917,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Karachi</t>
+          <t>JED</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Karachi</t>
+          <t>Jeddah</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>0315</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
@@ -4938,19 +4946,19 @@
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>WY241</t>
+          <t>PK172</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4960,22 +4968,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>PIA Pakistan International Airlines</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>Multan</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>Multan</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>0320</t>
+          <t>0230</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -4989,19 +4997,19 @@
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ET625</t>
+          <t>6E1274</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5011,22 +5019,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Ethiopian Airlines</t>
+          <t>6E</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Addis Ababa</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Addis Ababa</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>0425</t>
+          <t>0250</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -5040,19 +5048,19 @@
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>EK867</t>
+          <t>IX442</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5062,22 +5070,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Emirates</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>DXB</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>0440</t>
+          <t>0250</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
@@ -5091,19 +5099,19 @@
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>WY849</t>
+          <t>WY265</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5118,24 +5126,20 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Jakarta</t>
+          <t>Lucknow</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Jakarta</t>
+          <t>Lucknow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>0150</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>0235</t>
-        </is>
-      </c>
+          <t>0300</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
           <t>Departed</t>
@@ -5146,19 +5150,19 @@
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>TC409</t>
+          <t>6E1272</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5168,29 +5172,25 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>TC</t>
+          <t>6E</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Zanzibar</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Zanzibar</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>0350</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>0532</t>
-        </is>
-      </c>
+          <t>0300</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
           <t>Departed</t>
@@ -5201,19 +5201,19 @@
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>WY201</t>
+          <t>OV513</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5223,22 +5223,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Karachi</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Karachi</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>0505</t>
+          <t>0315</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
@@ -5252,19 +5252,19 @@
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>QR1149</t>
+          <t>WY241</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5274,22 +5274,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Qatar Airways</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>DOH</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Doha</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>0530</t>
+          <t>0320</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
@@ -5303,19 +5303,19 @@
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>OV391</t>
+          <t>ET625</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -5325,29 +5325,25 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Ethiopian Airlines</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Port Sudan</t>
+          <t>Addis Ababa</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Port Sudan</t>
+          <t>Addis Ababa</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>0705</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>0725</t>
-        </is>
-      </c>
+          <t>0425</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
           <t>Departed</t>
@@ -5358,19 +5354,19 @@
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>WY891</t>
+          <t>EK867</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5380,22 +5376,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Emirates</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>DXB</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>0800</t>
+          <t>0440</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
@@ -5409,19 +5405,19 @@
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>OV133</t>
+          <t>WY849</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -5431,27 +5427,27 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Duqm</t>
+          <t>Jakarta</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Duqm</t>
+          <t>Jakarta</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>0710</t>
+          <t>0150</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>0817</t>
+          <t>0235</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -5464,19 +5460,19 @@
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>OV5013</t>
+          <t>TC409</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -5486,27 +5482,27 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>TC</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Marmul</t>
+          <t>Zanzibar</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Marmul</t>
+          <t>Zanzibar</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>0810</t>
+          <t>0350</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>0857</t>
+          <t>0532</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -5519,19 +5515,19 @@
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>OV5011</t>
+          <t>WY201</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -5541,29 +5537,25 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Fahud</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Fahud</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>0820</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>0842</t>
-        </is>
-      </c>
+          <t>0505</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
           <t>Departed</t>
@@ -5574,19 +5566,19 @@
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>WY223</t>
+          <t>QR1149</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -5596,22 +5588,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Qatar Airways</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>DOH</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Doha</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>0825</t>
+          <t>0530</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
@@ -5625,19 +5617,19 @@
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>OV101</t>
+          <t>OV391</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -5652,20 +5644,24 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Port Sudan</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Port Sudan</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>0830</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr"/>
+          <t>0705</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>0725</t>
+        </is>
+      </c>
       <c r="H100" t="inlineStr">
         <is>
           <t>Departed</t>
@@ -5676,19 +5672,19 @@
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>WY815</t>
+          <t>WY891</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -5703,17 +5699,17 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>0840</t>
+          <t>0800</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
@@ -5727,19 +5723,19 @@
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>WY603</t>
+          <t>OV133</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -5749,25 +5745,29 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>DXB</t>
+          <t>Duqm</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Duqm</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>0840</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr"/>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>0817</t>
+        </is>
+      </c>
       <c r="H102" t="inlineStr">
         <is>
           <t>Departed</t>
@@ -5778,19 +5778,19 @@
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>OV283</t>
+          <t>OV5013</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -5805,17 +5805,17 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>JED</t>
+          <t>Marmul</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Jeddah</t>
+          <t>Marmul</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>0840</t>
+          <t>0810</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -5833,19 +5833,19 @@
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>WY903</t>
+          <t>OV5011</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -5855,25 +5855,29 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Fahud</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Fahud</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>0845</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr"/>
+          <t>0820</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>0842</t>
+        </is>
+      </c>
       <c r="H104" t="inlineStr">
         <is>
           <t>Departed</t>
@@ -5884,19 +5888,19 @@
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>WY823</t>
+          <t>WY223</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -5911,17 +5915,17 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Sepang</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Sepang</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>0845</t>
+          <t>0825</t>
         </is>
       </c>
       <c r="G105" t="inlineStr"/>
@@ -5935,19 +5939,19 @@
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>FZ046</t>
+          <t>OV101</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5957,22 +5961,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>flydubai</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>DXB</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>0910</t>
+          <t>0830</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
@@ -5986,19 +5990,19 @@
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>WY253</t>
+          <t>WY815</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6013,17 +6017,17 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>0920</t>
+          <t>0840</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
@@ -6037,19 +6041,19 @@
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>WY203</t>
+          <t>WY603</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6064,17 +6068,17 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>DXB</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>0920</t>
+          <t>0840</t>
         </is>
       </c>
       <c r="G108" t="inlineStr"/>
@@ -6088,19 +6092,19 @@
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>OV335</t>
+          <t>OV283</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -6115,20 +6119,24 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Baghdad</t>
+          <t>JED</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Baghdad</t>
+          <t>Jeddah</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>0940</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr"/>
+          <t>0840</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>0857</t>
+        </is>
+      </c>
       <c r="H109" t="inlineStr">
         <is>
           <t>Departed</t>
@@ -6139,19 +6147,19 @@
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>OV271</t>
+          <t>WY903</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -6161,22 +6169,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Medina</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Medina</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>0940</t>
+          <t>0845</t>
         </is>
       </c>
       <c r="G110" t="inlineStr"/>
@@ -6190,19 +6198,19 @@
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>G9113</t>
+          <t>WY823</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -6212,22 +6220,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Air Arabia</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Sharjah</t>
+          <t>Sepang</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sharjah</t>
+          <t>Sepang</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>0845</t>
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
@@ -6241,19 +6249,19 @@
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>OV341</t>
+          <t>FZ046</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -6263,22 +6271,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>flydubai</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Mogadishu</t>
+          <t>DXB</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Mogadishu</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>0910</t>
         </is>
       </c>
       <c r="G112" t="inlineStr"/>
@@ -6292,19 +6300,19 @@
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>WY245</t>
+          <t>WY253</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -6319,17 +6327,17 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>0920</t>
         </is>
       </c>
       <c r="G113" t="inlineStr"/>
@@ -6343,19 +6351,19 @@
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>OV365</t>
+          <t>WY203</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -6365,22 +6373,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Nairobi</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Nairobi</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>0920</t>
         </is>
       </c>
       <c r="G114" t="inlineStr"/>
@@ -6394,19 +6402,19 @@
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>WY831</t>
+          <t>OV335</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -6416,22 +6424,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Phuket</t>
+          <t>Baghdad</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Phuket</t>
+          <t>Baghdad</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>0940</t>
         </is>
       </c>
       <c r="G115" t="inlineStr"/>
@@ -6445,19 +6453,19 @@
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>OV5093</t>
+          <t>OV271</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -6472,17 +6480,17 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Mukhaizna Oil Field</t>
+          <t>Medina</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Mukhaizna Oil Field</t>
+          <t>Medina</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>0940</t>
         </is>
       </c>
       <c r="G116" t="inlineStr"/>
@@ -6496,19 +6504,19 @@
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>WY917</t>
+          <t>G9113</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -6518,22 +6526,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Air Arabia</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Sharjah</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Sharjah</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="G117" t="inlineStr"/>
@@ -6547,19 +6555,19 @@
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>EY693</t>
+          <t>OV341</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -6569,22 +6577,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Etihad Airways</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Abu Dhabi</t>
+          <t>Mogadishu</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Abu Dhabi</t>
+          <t>Mogadishu</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="G118" t="inlineStr"/>
@@ -6598,19 +6606,19 @@
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>OV103</t>
+          <t>WY245</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -6620,22 +6628,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="G119" t="inlineStr"/>
@@ -6649,19 +6657,19 @@
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>OV205</t>
+          <t>OV365</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -6676,17 +6684,17 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Riyadh</t>
+          <t>Nairobi</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Riyadh</t>
+          <t>Nairobi</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="G120" t="inlineStr"/>
@@ -6700,19 +6708,19 @@
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>WY165</t>
+          <t>WY831</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -6727,17 +6735,17 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Phuket</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Phuket</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="G121" t="inlineStr"/>
@@ -6751,19 +6759,19 @@
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>WY907</t>
+          <t>OV5093</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -6773,22 +6781,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Mukhaizna Oil Field</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Mukhaizna Oil Field</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="G122" t="inlineStr"/>
@@ -6802,19 +6810,19 @@
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>OV5015</t>
+          <t>WY917</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -6824,22 +6832,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Marmul</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Marmul</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="G123" t="inlineStr"/>
@@ -6853,19 +6861,19 @@
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>WY153</t>
+          <t>EY693</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -6875,22 +6883,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Etihad Airways</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Abu Dhabi</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Abu Dhabi</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="G124" t="inlineStr"/>
@@ -6904,19 +6912,19 @@
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>OV285</t>
+          <t>OV103</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -6931,17 +6939,17 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>JED</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Jeddah</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="G125" t="inlineStr"/>
@@ -6955,19 +6963,19 @@
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>WY683</t>
+          <t>OV205</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -6977,7 +6985,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6992,7 +7000,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="G126" t="inlineStr"/>
@@ -7006,12 +7014,1193 @@
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>2026-09-20 14:01</t>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>WY165</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>WY907</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>1320</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>OV5015</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>1330</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>WY153</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>OV285</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>WY683</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>1355</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>WY171</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>1310</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>WY131</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>1410</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>BG222</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Biman Bangladesh Airlines</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>1410</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>1425</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>WY101</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>1415</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>OV227</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Kuwait City</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Kuwait City</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>WY663</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>1435</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>WY405</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>1440</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>WY655</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Manama</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Manama</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>1445</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>WY675</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>1450</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>WY147</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Rome</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Rome</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>1505</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>WY143</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Ferno</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Ferno</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>1505</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>WY291</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>OV403</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>1530</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>6X6811</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>6X</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Tehran</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Tehran</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>1530</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>1553</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>OV315</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Al Jiza</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Al Jiza</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>1545</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>6X7313</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>6X</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Mashhad</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Mashhad</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>1630</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>OV213</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>20SEP</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Ad Dammam</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Ad Dammam</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>1630</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:26</t>
         </is>
       </c>
     </row>

--- a/flight_data/live_flights.xlsx
+++ b/flight_data/live_flights.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -512,6 +512,5424 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>IX236</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0015</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>OV761</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0025</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>OV401</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0115</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>OV795</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Jaipur</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Jaipur</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0140</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>WY685</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0145</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>WY849</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0150</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>WY251</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0205</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BS322</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0200</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0228</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>WY671</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>WY225</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>WY211</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>6E1274</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>IX442</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>WY265</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0300</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>6E1272</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0300</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>WY297</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0305</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>OV513</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0315</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>WY241</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0320</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TC409</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>TC</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Zanzibar</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Zanzibar</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0350</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ET625</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ethiopian Airlines</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0425</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Last Call</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>3T267</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>3T</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Khartoum</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Khartoum</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0430</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Last Call</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EK867</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Emirates</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0440</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Gate Closed</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PC831</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Pegasus Airlines</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Pendik, Istanbul</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Pendik, Istanbul</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>0435</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0505</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Gate Open</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>WY201</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0505</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Gate Open</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>QR1149</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Qatar Airways</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0530</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0630</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>OV5041</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>0745</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>WY223</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>0825</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>WY317</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>0825</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>OV133</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Duqm</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Duqm</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>0830</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>OV101</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>0830</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>OV811</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Vienna</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Vienna</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>0835</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>OV283</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>0840</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>WY815</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>0840</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>WY603</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>0840</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>WY903</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>0845</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>WY823</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>0845</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>OV241</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>0850</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>FZ046</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>flydubai</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>0910</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>WY705</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Zanzibar</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Zanzibar</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>0915</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>WY253</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>0920</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>OV271</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>0940</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>G9113</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Air Arabia</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>OV365</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>WY245</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>WY831</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Delayed</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>OV5093</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Mukhaizna Oil Field</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Mukhaizna Oil Field</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>EY693</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Etihad Airways</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>OV103</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>WY905</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>WY413</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Amman</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Amman</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>OV5043</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1330</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>OV285</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>WY153</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>WY683</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1355</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>OV337</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Baghdad</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Baghdad</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>PF735</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Rawalpindi</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Rawalpindi</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>BG122</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Biman Bangladesh Airlines</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>1410</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>WY101</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>1415</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>OV391</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Port Sudan</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Port Sudan</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>1420</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>OV227</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Kuwait City</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Kuwait City</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>WY609</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>WY663</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>1435</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>WY405</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>1440</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>WY675</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1450</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>WY679</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>1505</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>WY147</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Rome</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Rome</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1505</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>WY143</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Ferno</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Ferno</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>1505</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>WY291</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>OV403</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1530</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>WY907</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>1530</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>OV115</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>OV213</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Ad Dammam</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Ad Dammam</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>1630</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>OV771</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>WY909</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>1740</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>OV105</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>1850</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>WY681</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>1850</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>WY635</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>1850</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>WY647</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Kuwait City</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Kuwait City</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>1855</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>WY921</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>1940</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>G9119</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Air Arabia</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>1950</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>WY695</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Ad Dammam</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Ad Dammam</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>IX712</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Kannur</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Kannur</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>WY661</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>WY611</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>FZ048</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>flydubai</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2045</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>MU2052</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>China Eastern</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2115</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>IX164</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2115</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>MS931</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Egyptair</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2125</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>WY673</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2145</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>WY817</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2150</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>OV497</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2215</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>OV773</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2230</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>OV735</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2230</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>IX338</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>0005</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>OV563</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Rawalpindi</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Rawalpindi</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>QR1125</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Qatar Airways</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>WY407</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>IX620</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Tiruchirappalli</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Tiruchirappalli</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2315</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>OV783</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2320</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>OV705</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2320</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>IX550</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2325</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>EY697</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Etihad Airways</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2350</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>WY833</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2350</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>OV505</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Sialkot</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Sialkot</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2355</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>6E1268</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2355</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>GF567</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>23SEP</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Gulf Air</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Manama</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Manama</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2355</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:39</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/flight_data/live_flights.xlsx
+++ b/flight_data/live_flights.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -512,6 +512,830 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>OV761</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0025</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2026-09-24 00:01</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-09-24 00:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>OV421</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Sylhet</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sylhet</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0045</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-09-24 00:01</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-09-24 00:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>OV401</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0115</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0151</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-09-24 00:01</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-09-24 00:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>WY685</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0145</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-09-24 00:01</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-09-24 00:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>WY849</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0150</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026-09-24 00:01</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-09-24 00:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BS322</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0200</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-09-24 00:01</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-09-24 00:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TK775</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Turkish Airlines</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0130</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0210</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-09-24 00:01</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-09-24 00:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>WY251</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0205</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-09-24 00:01</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-09-24 00:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>WY225</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-09-24 00:01</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-09-24 00:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>WY211</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-09-24 00:01</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-09-24 00:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>6E1274</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2026-09-24 00:01</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-09-24 00:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>IX442</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2026-09-24 00:01</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-09-24 00:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>WY265</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0300</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-09-24 00:01</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-09-24 00:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>6E1272</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0300</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-09-24 00:01</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-09-24 00:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>OV513</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0315</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-09-24 00:01</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-09-24 00:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>IX236</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0015</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-09-24 00:01</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-09-24 00:01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/flight_data/live_flights.xlsx
+++ b/flight_data/live_flights.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -515,7 +515,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>OV761</t>
+          <t>ET625</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,22 +525,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Ethiopian Airlines</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Addis Ababa</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Addis Ababa</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0025</t>
+          <t>0425</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -554,19 +554,19 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-09-24 00:01</t>
+          <t>2026-09-24 04:32</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-09-24 00:01</t>
+          <t>2026-09-24 04:32</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>OV421</t>
+          <t>WY201</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -576,22 +576,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sylhet</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sylhet</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0505</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -605,19 +605,19 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-09-24 00:01</t>
+          <t>2026-09-24 04:32</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-09-24 00:01</t>
+          <t>2026-09-24 04:32</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>OV401</t>
+          <t>QR1149</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -627,29 +627,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Qatar Airways</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Chattogram</t>
+          <t>DOH</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chattogram</t>
+          <t>Doha</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0115</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0151</t>
-        </is>
-      </c>
+          <t>0530</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Departed</t>
@@ -660,19 +656,19 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-09-24 00:01</t>
+          <t>2026-09-24 04:32</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-09-24 00:01</t>
+          <t>2026-09-24 04:32</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WY685</t>
+          <t>OV287</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -682,22 +678,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Riyadh</t>
+          <t>JED</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Riyadh</t>
+          <t>Jeddah</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0145</t>
+          <t>0715</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -711,19 +707,19 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-09-24 00:01</t>
+          <t>2026-09-24 04:32</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-09-24 00:01</t>
+          <t>2026-09-24 04:32</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WY849</t>
+          <t>WY891</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -738,17 +734,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Jakarta</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jakarta</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0150</t>
+          <t>0800</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -762,19 +758,19 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-09-24 00:01</t>
+          <t>2026-09-24 04:32</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-09-24 00:01</t>
+          <t>2026-09-24 04:32</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BS322</t>
+          <t>OV5051</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -784,22 +780,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BS</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Marmul</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Marmul</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0200</t>
+          <t>0800</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -813,19 +809,19 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-09-24 00:01</t>
+          <t>2026-09-24 04:32</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-09-24 00:01</t>
+          <t>2026-09-24 04:32</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TK775</t>
+          <t>OV103</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -835,29 +831,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkish Airlines</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0130</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0210</t>
-        </is>
-      </c>
+          <t>0800</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Departed</t>
@@ -868,19 +860,19 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-09-24 00:01</t>
+          <t>2026-09-24 04:32</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-09-24 00:01</t>
+          <t>2026-09-24 04:32</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WY251</t>
+          <t>WY181</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -895,17 +887,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Sochi</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Sochi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0205</t>
+          <t>0810</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -919,19 +911,19 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-09-24 00:01</t>
+          <t>2026-09-24 04:32</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-09-24 00:01</t>
+          <t>2026-09-24 04:32</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WY225</t>
+          <t>WY223</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -956,13 +948,13 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0825</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Departed</t>
+          <t>Last Call</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -970,19 +962,19 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-09-24 00:01</t>
+          <t>2026-09-24 04:32</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-09-24 00:01</t>
+          <t>2026-09-24 04:32</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WY211</t>
+          <t>WY317</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -997,17 +989,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Thiruvananthapuram</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Thiruvananthapuram</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0825</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1021,19 +1013,19 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-09-24 00:01</t>
+          <t>2026-09-24 04:32</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-09-24 00:01</t>
+          <t>2026-09-24 04:32</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6E1274</t>
+          <t>OV283</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1043,28 +1035,28 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>6E</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>JED</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Jeddah</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0250</t>
+          <t>0840</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Departed</t>
+          <t>Last Call</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1072,19 +1064,19 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-09-24 00:01</t>
+          <t>2026-09-24 04:32</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-09-24 00:01</t>
+          <t>2026-09-24 04:32</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IX442</t>
+          <t>WY815</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1094,28 +1086,28 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0250</t>
+          <t>0840</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Departed</t>
+          <t>Last Call</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1123,19 +1115,19 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-09-24 00:01</t>
+          <t>2026-09-24 04:32</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-09-24 00:01</t>
+          <t>2026-09-24 04:32</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WY265</t>
+          <t>WY603</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1150,23 +1142,23 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Lucknow</t>
+          <t>DXB</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lucknow</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0300</t>
+          <t>0840</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Departed</t>
+          <t>Gate Open</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1174,19 +1166,19 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-09-24 00:01</t>
+          <t>2026-09-24 04:32</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-09-24 00:01</t>
+          <t>2026-09-24 04:32</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6E1272</t>
+          <t>WY903</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1196,28 +1188,28 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>6E</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0300</t>
+          <t>0845</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Departed</t>
+          <t>Gate Open</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1225,19 +1217,19 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-09-24 00:01</t>
+          <t>2026-09-24 04:32</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-09-24 00:01</t>
+          <t>2026-09-24 04:32</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>OV513</t>
+          <t>OV241</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1252,23 +1244,23 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Karachi</t>
+          <t>Sharjah</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Karachi</t>
+          <t>Sharjah</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0315</t>
+          <t>0850</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Departed</t>
+          <t>Gate Open</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -1276,19 +1268,19 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-09-24 00:01</t>
+          <t>2026-09-24 04:32</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-09-24 00:01</t>
+          <t>2026-09-24 04:32</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IX236</t>
+          <t>OV371</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1298,28 +1290,28 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Kigali</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Kigali</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0015</t>
+          <t>0900</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Departed</t>
+          <t>Gate Open</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -1327,12 +1319,4814 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-09-24 00:01</t>
+          <t>2026-09-24 04:32</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-09-24 00:01</t>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FZ046</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>flydubai</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0910</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Gate Open</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>WY843</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Manila</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Manila</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0915</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Gate Open</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>WY823</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0915</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Gate Open</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>WY203</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0920</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Gate Open</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>OV211</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Ad Dammam</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Ad Dammam</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0945</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>G9113</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Air Arabia</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>OV133</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Duqm</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Duqm</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>WY831</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>WY245</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>WY905</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>WY909</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1045</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>WY689</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>1055</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>EK863</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Emirates</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1125</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>OV5093</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Mukhaizna Oil Field</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Mukhaizna Oil Field</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>EY693</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Etihad Airways</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>WY933</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Khasab</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Khasab</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>OV205</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>OV105</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1245</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>WY165</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>WY171</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1310</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>OV285</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>OV273</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1345</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>WY683</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1355</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>OV337</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Baghdad</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Baghdad</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>OV135</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Duqm</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Duqm</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>OV293</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Abha</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Abha</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1410</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BG722</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Biman Bangladesh Airlines</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1410</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>WY131</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1410</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>WY101</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1415</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>OV227</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Kuwait City</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Kuwait City</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>WY693</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Ad Dammam</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Ad Dammam</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>WY609</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>WY663</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1435</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>WY405</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1440</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>WY675</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1450</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>WY291</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>OV403</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1530</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>WY907</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1530</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>OV5141</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Masirah</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Masirah</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>1545</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>OV315</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Al Jiza</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Al Jiza</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1550</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>WY183</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>1555</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>OV115</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>OV245</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>1720</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>WY669</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>1805</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>PK230</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>PIA Pakistan International Airlines</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Lahore</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Lahore</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>1830</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>WY681</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>1850</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>WY647</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Kuwait City</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Kuwait City</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>1855</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>OV497</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1915</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>WY653</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Manama</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Manama</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>1915</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>OV107</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1930</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>WY921</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>1940</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>G9119</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Air Arabia</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>1950</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>WY661</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>WY611</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>WY411</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Amman</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Amman</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>FZ048</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>flydubai</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2045</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>IX164</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2115</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>WY821</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2120</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>MS931</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Egyptair</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2140</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>WY677</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2140</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>WY673</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2145</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>WY817</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2150</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>OV437</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Colombo</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Colombo</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2215</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>OV773</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2230</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>OV735</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2230</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>IX338</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2235</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>IX236</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>0015</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>OV563</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Rawalpindi</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Rawalpindi</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>OV521</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Lahore</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Lahore</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>QR1125</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Qatar Airways</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>WY833</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>WY707</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Dar es Salaam</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Dar es Salaam</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2305</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>IX550</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2325</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>EY697</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Etihad Airways</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2350</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>OV537</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Multan</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Multan</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2355</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>6E1268</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2355</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>GF567</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Gulf Air</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Manama</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Manama</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2355</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>OV761</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>0025</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>OV421</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Sylhet</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Sylhet</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>0045</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>OV401</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>0115</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>0151</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>WY685</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>0145</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>WY849</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>0150</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>BS322</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>0200</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>TK775</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Turkish Airlines</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>0130</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>0210</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>WY251</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>0205</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>WY225</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>WY211</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>6E1274</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>IX442</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>WY265</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>0300</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>6E1272</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>0300</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>OV513</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>0315</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>WY241</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>0320</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>OV341</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>24SEP</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Mogadishu</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Mogadishu</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>0330</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:32</t>
         </is>
       </c>
     </row>

--- a/flight_data/live_flights.xlsx
+++ b/flight_data/live_flights.xlsx
@@ -515,7 +515,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ET625</t>
+          <t>FZ046</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,22 +525,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ethiopian Airlines</t>
+          <t>flydubai</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Addis Ababa</t>
+          <t>DXB</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Addis Ababa</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0425</t>
+          <t>0910</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -554,19 +554,19 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WY201</t>
+          <t>WY843</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -581,17 +581,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Manila</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Manila</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0505</t>
+          <t>0915</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -605,19 +605,19 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>QR1149</t>
+          <t>WY823</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -627,22 +627,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Qatar Airways</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DOH</t>
+          <t>Sepang</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Doha</t>
+          <t>Sepang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0530</t>
+          <t>0915</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -656,19 +656,19 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OV287</t>
+          <t>WY203</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -678,22 +678,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>JED</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeddah</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0715</t>
+          <t>0920</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -707,19 +707,19 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WY891</t>
+          <t>OV211</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -729,22 +729,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Ad Dammam</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Ad Dammam</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0800</t>
+          <t>0945</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -758,19 +758,19 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OV5051</t>
+          <t>OV133</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -785,17 +785,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Marmul</t>
+          <t>Duqm</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Marmul</t>
+          <t>Duqm</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0800</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -809,19 +809,19 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OV103</t>
+          <t>G9113</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -831,25 +831,29 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Air Arabia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Sharjah</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Sharjah</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0800</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1026</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Departed</t>
@@ -860,19 +864,19 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WY181</t>
+          <t>WY831</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -887,17 +891,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sochi</t>
+          <t>Phuket</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sochi</t>
+          <t>Phuket</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0810</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -911,19 +915,19 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WY223</t>
+          <t>WY245</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -938,23 +942,23 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0825</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Last Call</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -962,19 +966,19 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WY317</t>
+          <t>WY905</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -989,17 +993,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0825</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1013,19 +1017,19 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>OV283</t>
+          <t>WY909</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1035,28 +1039,28 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>JED</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jeddah</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0840</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Last Call</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1064,19 +1068,19 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WY815</t>
+          <t>WY689</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1091,23 +1095,23 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>JED</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Jeddah</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0840</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Last Call</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1115,19 +1119,19 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WY603</t>
+          <t>EK863</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1137,7 +1141,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Emirates</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1152,13 +1156,13 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0840</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Gate Open</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1166,19 +1170,19 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WY903</t>
+          <t>OV5093</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1188,28 +1192,28 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Mukhaizna Oil Field</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Mukhaizna Oil Field</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0845</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Gate Open</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1217,19 +1221,19 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>OV241</t>
+          <t>EY693</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1239,28 +1243,28 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Etihad Airways</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sharjah</t>
+          <t>Abu Dhabi</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sharjah</t>
+          <t>Abu Dhabi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0850</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Gate Open</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -1268,19 +1272,19 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>OV371</t>
+          <t>WY933</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1290,28 +1294,28 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Kigali</t>
+          <t>Khasab</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kigali</t>
+          <t>Khasab</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0900</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Gate Open</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -1319,19 +1323,19 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FZ046</t>
+          <t>OV205</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1341,28 +1345,28 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>flydubai</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DXB</t>
+          <t>Riyadh</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Riyadh</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0910</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Gate Open</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -1370,19 +1374,19 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>WY843</t>
+          <t>OV105</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1392,28 +1396,32 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Manila</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Manila</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0915</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>1245</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1306</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Gate Open</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -1421,19 +1429,19 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>WY823</t>
+          <t>WY165</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1448,23 +1456,23 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sepang</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sepang</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0915</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Gate Open</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -1472,19 +1480,19 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>WY203</t>
+          <t>WY171</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1499,23 +1507,23 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Amsterdam</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Amsterdam</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0920</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Gate Open</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -1523,19 +1531,19 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>OV211</t>
+          <t>OV285</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1550,23 +1558,23 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ad Dammam</t>
+          <t>JED</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ad Dammam</t>
+          <t>Jeddah</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0945</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Last Call</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -1574,19 +1582,19 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>G9113</t>
+          <t>OV273</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1596,28 +1604,28 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Air Arabia</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sharjah</t>
+          <t>Medina</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sharjah</t>
+          <t>Medina</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1345</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Last Call</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -1625,19 +1633,19 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>OV133</t>
+          <t>WY683</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1647,28 +1655,28 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Duqm</t>
+          <t>Riyadh</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Duqm</t>
+          <t>Riyadh</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Last Call</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -1676,19 +1684,19 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>WY831</t>
+          <t>OV337</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1698,28 +1706,28 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Phuket</t>
+          <t>Baghdad</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Phuket</t>
+          <t>Baghdad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Gate Open</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -1727,19 +1735,19 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>WY245</t>
+          <t>OV135</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1749,28 +1757,28 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>Duqm</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>Duqm</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Last Call</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -1778,19 +1786,19 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>WY905</t>
+          <t>OV293</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1800,28 +1808,28 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Abha</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Abha</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Gate Open</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -1829,19 +1837,19 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>WY909</t>
+          <t>WY131</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1856,23 +1864,23 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Gate Open</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -1880,19 +1888,19 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>WY689</t>
+          <t>BG722</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1902,28 +1910,28 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Biman Bangladesh Airlines</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>JED</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Jeddah</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Gate Open</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -1931,19 +1939,19 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EK863</t>
+          <t>WY101</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1953,28 +1961,28 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Emirates</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DXB</t>
+          <t>LHR</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>London</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Gate Open</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -1982,19 +1990,19 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>OV5093</t>
+          <t>WY693</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2004,22 +2012,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Mukhaizna Oil Field</t>
+          <t>Ad Dammam</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Mukhaizna Oil Field</t>
+          <t>Ad Dammam</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -2033,19 +2041,19 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>EY693</t>
+          <t>WY609</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2055,28 +2063,28 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Etihad Airways</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Abu Dhabi</t>
+          <t>DXB</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Abu Dhabi</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Delayed</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -2084,19 +2092,19 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>WY933</t>
+          <t>OV227</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2106,22 +2114,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Khasab</t>
+          <t>Kuwait City</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Khasab</t>
+          <t>Kuwait City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -2135,19 +2143,19 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>OV205</t>
+          <t>WY663</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2157,22 +2165,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Riyadh</t>
+          <t>DOH</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Riyadh</t>
+          <t>Doha</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -2186,19 +2194,19 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>OV105</t>
+          <t>WY405</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2208,22 +2216,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Cairo</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Cairo</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -2237,19 +2245,19 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>WY165</t>
+          <t>WY675</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2264,17 +2272,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>JED</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Jeddah</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -2288,19 +2296,19 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>WY171</t>
+          <t>WY291</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2315,23 +2323,23 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>Calicut</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>Calicut</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Delayed</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -2339,19 +2347,19 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>OV285</t>
+          <t>OV403</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2366,17 +2374,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>JED</t>
+          <t>Chattogram</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Jeddah</t>
+          <t>Chattogram</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1530</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -2390,19 +2398,19 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>OV273</t>
+          <t>WY907</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2412,22 +2420,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Medina</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Medina</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>1530</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -2441,19 +2449,19 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>WY683</t>
+          <t>OV5141</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2463,22 +2471,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Riyadh</t>
+          <t>Masirah</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Riyadh</t>
+          <t>Masirah</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1545</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -2492,19 +2500,19 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>OV337</t>
+          <t>OV315</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2519,17 +2527,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Baghdad</t>
+          <t>Al Jiza</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Baghdad</t>
+          <t>Al Jiza</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1550</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -2543,19 +2551,19 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>OV135</t>
+          <t>WY183</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2565,28 +2573,28 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Duqm</t>
+          <t>Moscow</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Duqm</t>
+          <t>Moscow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1555</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Delayed</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -2594,19 +2602,19 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>OV293</t>
+          <t>OV115</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2621,17 +2629,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Abha</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Abha</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -2645,19 +2653,19 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BG722</t>
+          <t>OV245</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2667,22 +2675,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Biman Bangladesh Airlines</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Sharjah</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Sharjah</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>1720</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -2696,19 +2704,19 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>WY131</t>
+          <t>WY669</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2723,17 +2731,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>DOH</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Doha</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -2747,19 +2755,19 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>WY101</t>
+          <t>PK230</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2769,22 +2777,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>PIA Pakistan International Airlines</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LHR</t>
+          <t>Lahore</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Lahore</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -2798,19 +2806,19 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>OV227</t>
+          <t>WY681</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2820,22 +2828,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Kuwait City</t>
+          <t>Riyadh</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kuwait City</t>
+          <t>Riyadh</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -2849,19 +2857,19 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>WY693</t>
+          <t>WY647</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2876,23 +2884,23 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Ad Dammam</t>
+          <t>Kuwait City</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ad Dammam</t>
+          <t>Kuwait City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Delayed</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -2900,19 +2908,19 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>WY609</t>
+          <t>OV497</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2922,22 +2930,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>DXB</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -2951,19 +2959,19 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>WY663</t>
+          <t>WY653</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2978,17 +2986,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>DOH</t>
+          <t>Manama</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Doha</t>
+          <t>Manama</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -3002,19 +3010,19 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>WY405</t>
+          <t>OV107</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3024,22 +3032,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Cairo</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Cairo</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>1930</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -3053,19 +3061,19 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>WY675</t>
+          <t>WY921</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3080,17 +3088,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>JED</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Jeddah</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -3104,19 +3112,19 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>WY291</t>
+          <t>G9119</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3126,22 +3134,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Air Arabia</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Calicut</t>
+          <t>Sharjah</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Calicut</t>
+          <t>Sharjah</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -3155,19 +3163,19 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>OV403</t>
+          <t>WY661</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3177,22 +3185,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Chattogram</t>
+          <t>DOH</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Chattogram</t>
+          <t>Doha</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1530</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -3206,19 +3214,19 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>WY907</t>
+          <t>WY611</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3233,17 +3241,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>DXB</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1530</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -3257,19 +3265,19 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>OV5141</t>
+          <t>WY411</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3279,22 +3287,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Masirah</t>
+          <t>Amman</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Masirah</t>
+          <t>Amman</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1545</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -3308,19 +3316,19 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>OV315</t>
+          <t>FZ048</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3330,22 +3338,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>flydubai</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Al Jiza</t>
+          <t>DXB</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Jiza</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -3359,19 +3367,19 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>WY183</t>
+          <t>IX164</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3381,22 +3389,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Moscow</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Moscow</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1555</t>
+          <t>2115</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -3410,19 +3418,19 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>OV115</t>
+          <t>WY821</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3432,22 +3440,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Sepang</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Sepang</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2120</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -3461,19 +3469,19 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>OV245</t>
+          <t>MS931</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3483,22 +3491,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Egyptair</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Sharjah</t>
+          <t>Cairo</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sharjah</t>
+          <t>Cairo</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1720</t>
+          <t>2140</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -3512,19 +3520,19 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>WY669</t>
+          <t>WY677</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3539,17 +3547,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>DOH</t>
+          <t>Medina</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Doha</t>
+          <t>Medina</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>2140</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -3563,19 +3571,19 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PK230</t>
+          <t>WY673</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3585,22 +3593,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>PIA Pakistan International Airlines</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Lahore</t>
+          <t>JED</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Lahore</t>
+          <t>Jeddah</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1830</t>
+          <t>2145</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -3614,19 +3622,19 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>WY681</t>
+          <t>WY817</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3641,17 +3649,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Riyadh</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Riyadh</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -3665,19 +3673,19 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>WY647</t>
+          <t>OV437</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3687,22 +3695,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Kuwait City</t>
+          <t>Colombo</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kuwait City</t>
+          <t>Colombo</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
@@ -3716,19 +3724,19 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>OV497</t>
+          <t>OV773</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3743,17 +3751,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Calicut</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Calicut</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>2230</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -3767,19 +3775,19 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>WY653</t>
+          <t>OV735</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3789,22 +3797,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Manama</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Manama</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>2230</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -3818,19 +3826,19 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>OV107</t>
+          <t>IX338</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3840,22 +3848,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Calicut</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Calicut</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>2235</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -3869,19 +3877,19 @@
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>WY921</t>
+          <t>IX236</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3891,28 +3899,28 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>0015</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -3920,19 +3928,19 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>G9119</t>
+          <t>OV563</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3942,22 +3950,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Air Arabia</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Sharjah</t>
+          <t>Rawalpindi</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sharjah</t>
+          <t>Rawalpindi</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -3971,19 +3979,19 @@
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>WY661</t>
+          <t>OV521</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3993,22 +4001,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>DOH</t>
+          <t>Lahore</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Doha</t>
+          <t>Lahore</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -4022,19 +4030,19 @@
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>WY611</t>
+          <t>QR1125</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4044,22 +4052,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Qatar Airways</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>DXB</t>
+          <t>DOH</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Doha</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -4073,19 +4081,19 @@
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>WY411</t>
+          <t>WY833</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4100,17 +4108,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Amman</t>
+          <t>Phuket</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Amman</t>
+          <t>Phuket</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -4124,19 +4132,19 @@
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FZ048</t>
+          <t>WY707</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4146,22 +4154,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>flydubai</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>DXB</t>
+          <t>Dar es Salaam</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Dar es Salaam</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -4175,19 +4183,19 @@
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>IX164</t>
+          <t>IX550</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4202,17 +4210,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>Thiruvananthapuram</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>Thiruvananthapuram</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2115</t>
+          <t>2325</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -4226,19 +4234,19 @@
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>WY821</t>
+          <t>EY697</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4248,22 +4256,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Etihad Airways</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Sepang</t>
+          <t>Abu Dhabi</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sepang</t>
+          <t>Abu Dhabi</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -4277,19 +4285,19 @@
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MS931</t>
+          <t>OV537</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4299,22 +4307,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Egyptair</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Cairo</t>
+          <t>Multan</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Cairo</t>
+          <t>Multan</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2140</t>
+          <t>2355</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
@@ -4328,19 +4336,19 @@
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>WY677</t>
+          <t>6E1268</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4350,22 +4358,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>6E</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Medina</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Medina</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2140</t>
+          <t>2355</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -4379,19 +4387,19 @@
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>WY673</t>
+          <t>GF567</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4401,22 +4409,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Gulf Air</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>JED</t>
+          <t>Manama</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Jeddah</t>
+          <t>Manama</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>2355</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
@@ -4430,19 +4438,19 @@
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>WY817</t>
+          <t>OV761</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4452,28 +4460,28 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>0025</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -4481,19 +4489,19 @@
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>OV437</t>
+          <t>OV421</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4508,23 +4516,23 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Colombo</t>
+          <t>Sylhet</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Colombo</t>
+          <t>Sylhet</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2215</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -4532,19 +4540,19 @@
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>OV773</t>
+          <t>OV401</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4559,23 +4567,27 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Calicut</t>
+          <t>Chattogram</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Calicut</t>
+          <t>Chattogram</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2230</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr"/>
+          <t>0115</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>0151</t>
+        </is>
+      </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -4583,19 +4595,19 @@
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>OV735</t>
+          <t>WY685</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4605,28 +4617,28 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Riyadh</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Riyadh</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>0145</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -4634,19 +4646,19 @@
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>IX338</t>
+          <t>WY849</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4656,28 +4668,28 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Calicut</t>
+          <t>Jakarta</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Calicut</t>
+          <t>Jakarta</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2235</t>
+          <t>0150</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -4685,19 +4697,19 @@
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>IX236</t>
+          <t>BS322</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4707,22 +4719,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>BS</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>0015</t>
+          <t>0200</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
@@ -4736,19 +4748,19 @@
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>OV563</t>
+          <t>TK775</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4758,28 +4770,32 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Turkish Airlines</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Rawalpindi</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Rawalpindi</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2300</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr"/>
+          <t>0130</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>0210</t>
+        </is>
+      </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -4787,19 +4803,19 @@
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>OV521</t>
+          <t>WY251</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4809,28 +4825,28 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Lahore</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Lahore</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>0205</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -4838,19 +4854,19 @@
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>QR1125</t>
+          <t>WY225</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4860,28 +4876,28 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Qatar Airways</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>DOH</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Doha</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -4889,19 +4905,19 @@
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>WY833</t>
+          <t>WY211</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4916,23 +4932,23 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Phuket</t>
+          <t>Thiruvananthapuram</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Phuket</t>
+          <t>Thiruvananthapuram</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -4940,19 +4956,19 @@
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>WY707</t>
+          <t>6E1274</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4962,28 +4978,28 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>6E</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Dar es Salaam</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Dar es Salaam</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>0250</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -4991,19 +5007,19 @@
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>IX550</t>
+          <t>IX442</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5018,23 +5034,23 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Thiruvananthapuram</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Thiruvananthapuram</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2325</t>
+          <t>0250</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -5042,19 +5058,19 @@
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>EY697</t>
+          <t>WY265</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5064,28 +5080,28 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Etihad Airways</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Abu Dhabi</t>
+          <t>Lucknow</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Abu Dhabi</t>
+          <t>Lucknow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2350</t>
+          <t>0300</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -5093,19 +5109,19 @@
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>OV537</t>
+          <t>6E1272</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5115,28 +5131,28 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>6E</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Multan</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Multan</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2355</t>
+          <t>0300</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -5144,19 +5160,19 @@
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>6E1268</t>
+          <t>OV513</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5166,28 +5182,28 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>6E</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Karachi</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Karachi</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2355</t>
+          <t>0315</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -5195,19 +5211,19 @@
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>GF567</t>
+          <t>WY241</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -5217,28 +5233,28 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Gulf Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Manama</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Manama</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2355</t>
+          <t>0320</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -5246,19 +5262,19 @@
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>OV761</t>
+          <t>OV341</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5273,17 +5289,17 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Mogadishu</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Mogadishu</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>0025</t>
+          <t>0330</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
@@ -5297,19 +5313,19 @@
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>OV421</t>
+          <t>ET625</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -5319,22 +5335,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Ethiopian Airlines</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Sylhet</t>
+          <t>Addis Ababa</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sylhet</t>
+          <t>Addis Ababa</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0425</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
@@ -5348,19 +5364,19 @@
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>OV401</t>
+          <t>WY201</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -5370,29 +5386,25 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Chattogram</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Chattogram</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>0115</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>0151</t>
-        </is>
-      </c>
+          <t>0505</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
           <t>Departed</t>
@@ -5403,19 +5415,19 @@
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>WY685</t>
+          <t>QR1149</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -5425,22 +5437,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Qatar Airways</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Riyadh</t>
+          <t>DOH</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Riyadh</t>
+          <t>Doha</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>0145</t>
+          <t>0530</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
@@ -5454,19 +5466,19 @@
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>WY849</t>
+          <t>OV287</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -5476,22 +5488,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Jakarta</t>
+          <t>JED</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Jakarta</t>
+          <t>Jeddah</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>0150</t>
+          <t>0715</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
@@ -5505,19 +5517,19 @@
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>BS322</t>
+          <t>WY891</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -5527,22 +5539,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>BS</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>0200</t>
+          <t>0800</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
@@ -5556,19 +5568,19 @@
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>TK775</t>
+          <t>OV5051</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -5578,29 +5590,25 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Turkish Airlines</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Marmul</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Marmul</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>0130</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>0210</t>
-        </is>
-      </c>
+          <t>0800</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
           <t>Departed</t>
@@ -5611,19 +5619,19 @@
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>WY251</t>
+          <t>OV103</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -5633,22 +5641,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>0205</t>
+          <t>0800</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
@@ -5662,19 +5670,19 @@
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>WY225</t>
+          <t>WY181</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -5689,17 +5697,17 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Sochi</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Sochi</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0810</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
@@ -5713,19 +5721,19 @@
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>WY211</t>
+          <t>WY223</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -5740,17 +5748,17 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Thiruvananthapuram</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Thiruvananthapuram</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0825</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
@@ -5764,19 +5772,19 @@
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>6E1274</t>
+          <t>WY317</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -5786,22 +5794,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>6E</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>0250</t>
+          <t>0825</t>
         </is>
       </c>
       <c r="G105" t="inlineStr"/>
@@ -5815,19 +5823,19 @@
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>IX442</t>
+          <t>WY815</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5837,22 +5845,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>0250</t>
+          <t>0840</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
@@ -5866,19 +5874,19 @@
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>WY265</t>
+          <t>WY603</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5893,17 +5901,17 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Lucknow</t>
+          <t>DXB</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Lucknow</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>0300</t>
+          <t>0840</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
@@ -5917,19 +5925,19 @@
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>6E1272</t>
+          <t>OV283</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5939,22 +5947,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>6E</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>JED</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Jeddah</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>0300</t>
+          <t>0840</t>
         </is>
       </c>
       <c r="G108" t="inlineStr"/>
@@ -5968,19 +5976,19 @@
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>OV513</t>
+          <t>WY903</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5990,22 +5998,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Karachi</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Karachi</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>0315</t>
+          <t>0845</t>
         </is>
       </c>
       <c r="G109" t="inlineStr"/>
@@ -6019,19 +6027,19 @@
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>WY241</t>
+          <t>OV241</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -6041,22 +6049,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>Sharjah</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>Sharjah</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>0320</t>
+          <t>0850</t>
         </is>
       </c>
       <c r="G110" t="inlineStr"/>
@@ -6070,19 +6078,19 @@
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>OV341</t>
+          <t>OV371</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -6097,17 +6105,17 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Mogadishu</t>
+          <t>Kigali</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Mogadishu</t>
+          <t>Kigali</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>0330</t>
+          <t>0900</t>
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
@@ -6121,12 +6129,12 @@
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>2026-09-24 04:32</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
     </row>

--- a/flight_data/live_flights.xlsx
+++ b/flight_data/live_flights.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -512,6 +512,9245 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TK774</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Turkish Airlines</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0030</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0114</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BS321</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0100</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PK171</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PIA Pakistan International Airlines</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Multan</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Multan</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0115</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>WY662</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0130</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>OV772</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0135</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6E1273</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0150</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>IX441</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0150</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>6E1271</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0200</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>On Time</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>OV404</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0215</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TC408</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>TC</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Dar es Salaam</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Dar es Salaam</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0220</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EK866</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Emirates</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0330</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ET624</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ethiopian Airlines</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0335</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>QR1148</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Qatar Airways</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0355</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>WY412</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Amman</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Amman</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0405</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>WY118</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0405</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>WY124</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0445</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>WY678</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0510</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>WY172</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0515</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>OV522</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Lahore</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Lahore</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0540</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>OV564</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Rawalpindi</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Rawalpindi</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0545</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>OV538</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Multan</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Multan</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0545</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>OV774</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0605</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>OV736</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>0605</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>WY674</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0630</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>OV506</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Sialkot</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sialkot</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0635</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>OV762</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>0650</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>WY102</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>0700</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>WY686</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>OV706</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>0715</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>OV514</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>0730</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>OV438</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Colombo</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Colombo</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>0735</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>WY184</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>0740</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>FZ045</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>flydubai</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>0810</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>OV498</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>0835</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>G9112</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Air Arabia</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>0910</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>WY672</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>0950</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>OV134</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Duqm</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Duqm</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>WY252</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1035</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>EY692</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Etihad Airways</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>WY242</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1045</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>WY266</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1055</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>WY202</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>WY818</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1150</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>OV402</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>WY844</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Manila</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Manila</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>WY822</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>WY282</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>OV242</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1210</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>OV102</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>WY604</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>BG721</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Biman Bangladesh Airlines</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1220</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>OV5014</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1225</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>WY707</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Zanzibar</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Zanzibar</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1225</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>WY904</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>OV5012</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Fahud</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Fahud</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>OV5094</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Mukhaizna Oil Field</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Mukhaizna Oil Field</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1445</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>OV392</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Port Sudan</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Port Sudan</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>1505</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>WY204</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>1545</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>OV284</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>1620</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>WY224</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>1640</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>OV5016</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>1645</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>OV272</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>1645</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>OV104</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>OV336</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Baghdad</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Baghdad</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1715</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>WY254</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>1750</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>WY246</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1750</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>OV206</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>1805</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>WY664</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>1840</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>MU2051</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>China Eastern</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1855</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>G9118</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Air Arabia</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>1900</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>WY850</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>IX711</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Kannur</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Kannur</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>OV342</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Mogadishu</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Mogadishu</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>1915</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>WY684</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>1920</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>FZ047</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>flydubai</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>1945</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>OV228</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Kuwait City</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Kuwait City</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>IX163</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>MS930</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Egyptair</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>OV246</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>OV214</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Ad Dammam</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Ad Dammam</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>WY624</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2110</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>OV366</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2110</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>OV286</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2115</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>WY918</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2115</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>QR1124</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Qatar Airways</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2130</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>OV106</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2145</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>OV316</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Al Jiza</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Al Jiza</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>0005</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>WY166</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>WY682</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>0015</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>WY916</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>0045</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>OV401</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>0115</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>WY685</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>0145</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>WY849</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>0150</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>TK775</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Turkish Airlines</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>0130</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>0213</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Delayed</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>BS322</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>0200</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>WY251</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>0205</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>WY671</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>PK172</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>PIA Pakistan International Airlines</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Multan</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Multan</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>0230</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>6E1274</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>IX442</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>WY265</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>0300</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>6E1272</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>0300</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>OV513</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>0315</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>WY241</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>0320</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>TC409</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>TC</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Zanzibar</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Zanzibar</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>0350</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>WY281</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>0400</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>ET625</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Ethiopian Airlines</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>0425</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>EK867</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Emirates</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>0440</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>WY201</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>0505</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>QR1149</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Qatar Airways</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>0530</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>OV391</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Port Sudan</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Port Sudan</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>0705</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>OV133</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Duqm</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Duqm</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>WY891</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>0800</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>OV5013</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>0810</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>OV5011</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Fahud</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Fahud</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>0820</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>WY223</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>0825</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>OV101</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>0830</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>OV283</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>0840</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>WY815</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>0840</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>WY603</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>0840</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>WY903</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>0845</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>WY823</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>0845</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>OV241</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>0850</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>FZ046</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>flydubai</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>0910</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>WY843</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Manila</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Manila</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>0915</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>WY253</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>0920</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>WY203</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>0920</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>OV335</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Baghdad</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Baghdad</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>0940</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>OV271</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>0940</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>G9113</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Air Arabia</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>OV341</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Mogadishu</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Mogadishu</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>OV365</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>WY245</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>WY831</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>OV5093</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Mukhaizna Oil Field</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Mukhaizna Oil Field</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>WY917</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>EY693</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Etihad Airways</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>OV205</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>WY165</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>WY171</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>1310</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>OV103</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>1315</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>OV5015</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>1330</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>OV285</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>WY153</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>WY683</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>1355</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>BG222</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Biman Bangladesh Airlines</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>1410</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>WY131</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>1410</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>WY101</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>1415</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>OV227</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Kuwait City</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Kuwait City</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>WY663</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>1435</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>WY405</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>1440</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>WY675</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>1450</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>WY147</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Rome</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Rome</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>1505</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>WY143</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Ferno</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Ferno</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>1505</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>WY291</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>OV403</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>1530</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>OV315</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Al Jiza</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Al Jiza</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>1530</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>OV213</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Ad Dammam</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Ad Dammam</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>1630</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>OV245</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>1720</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>OV901</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Beringin</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Beringin</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>1745</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>WY623</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>1745</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>OV105</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>WY681</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>1850</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>WY635</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>1850</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>WY647</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Kuwait City</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Kuwait City</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>1855</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>OV497</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>1915</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>OV107</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>1930</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>WY669</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>1935</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>WY921</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>1940</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>G9119</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Air Arabia</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>1950</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>IX712</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Kannur</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Kannur</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>WY661</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>WY611</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>FZ048</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>flydubai</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2045</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>WY821</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>MU2052</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>China Eastern</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2115</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>IX164</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>2115</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>MS931</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Egyptair</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>2125</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>WY817</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>2150</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>IX236</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>0015</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>OV761</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>27SEP</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>0025</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/flight_data/live_flights.xlsx
+++ b/flight_data/live_flights.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -512,6 +512,9740 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>OV316</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Al Jiza</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Al Jiza</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0050</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>6E1273</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0150</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>IX441</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0150</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>6E1271</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0200</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>OV404</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0215</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>EK866</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Emirates</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0330</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0313</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PC830</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Pegasus Airlines</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Pendik, Istanbul</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Pendik, Istanbul</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0330</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ET624</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ethiopian Airlines</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0335</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>QR1148</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Qatar Airways</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0355</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>WY678</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0510</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>WY172</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0515</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Arrived</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>WY674</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0525</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>On Time</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>WY154</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0525</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Bags on Belt</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>OV498</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0535</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0508</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Arrived</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>WY148</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Rome</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Rome</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0545</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>OV736</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0605</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>On Time</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>OV774</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0605</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>On Time</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>WY144</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Ferno</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Ferno</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0605</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>OV598</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Peshawar</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Peshawar</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0620</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>WY132</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0620</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>OV762</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0650</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>On Time</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>OV706</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0715</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0645</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>WY102</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>0700</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>On Time</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>OV784</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>On Time</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>OV514</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0730</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>OV902</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Beringin</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Beringin</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>0730</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>On Time</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>6Q781</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>6Q</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Damascus</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Damascus</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>0800</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>FZ045</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>flydubai</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>0810</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>OV796</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Jaipur</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Jaipur</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>0845</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>G9112</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Air Arabia</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>0910</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>WY672</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>0950</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>WY252</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1035</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>WY226</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>EY692</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Etihad Airways</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>WY242</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1045</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>WY212</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1050</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>WY266</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1055</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>OV134</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Duqm</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Duqm</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>WY818</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1150</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>OV402</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>WY844</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Manila</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Manila</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>On Time</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>WY282</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>OV242</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1210</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>OV102</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>WY822</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>WY604</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>OV5024</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1225</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>WY904</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>OV5022</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Fahud</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Fahud</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>WY834</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>PF736</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Sialkot</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Sialkot</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1425</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>OV288</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>WY204</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1545</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>OV104</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>OV284</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>1620</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>WY224</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1640</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>OV272</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>1645</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>OV336</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Baghdad</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Baghdad</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>1715</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>OV5026</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>1750</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>WY246</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>1750</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>OV206</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>WY610</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>1825</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>WY104</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>1835</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>WY664</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1840</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>WY318</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>1850</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>WY656</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Manama</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Manama</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1855</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>G9118</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Air Arabia</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>1900</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>WY850</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>IX711</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Kannur</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Kannur</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>WY684</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>1920</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>WY908</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1925</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>FZ047</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>flydubai</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>1945</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>OV228</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Kuwait City</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Kuwait City</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>IX163</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>OV246</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>WY414</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Amman</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Amman</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2045</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>OV214</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Ad Dammam</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Ad Dammam</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>OV366</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2110</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>OV286</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2115</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>OV106</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2115</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>QR1124</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Qatar Airways</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2130</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>OV928</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Almaty</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Almaty</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2045</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2215</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>WY816</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2200</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>EY696</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Etihad Airways</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2200</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>WY670</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2210</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>WY636</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2210</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>WY676</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2215</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>OV812</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Vienna</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Vienna</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2220</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>IX549</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2225</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>OV392</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Port Sudan</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Port Sudan</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2235</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>6E1267</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2255</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>On Time</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>WY892</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>WY824</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>WY166</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>WY682</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>0015</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>WY662</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>0015</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>WY832</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>0025</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>TK774</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Turkish Airlines</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>0030</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>0058</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>BS321</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>0100</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>OV401</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>0115</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>WY103</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>0135</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>WY849</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>0150</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>WY251</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>0205</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>TK775</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Turkish Airlines</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>0130</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>0204</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>OV795</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Jaipur</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Jaipur</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>0150</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>BS322</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>0200</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>WY671</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>WY225</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>WY211</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>6E1274</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>IX442</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>WY265</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>0300</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>6E1272</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>0300</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>OV513</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>0315</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>0344</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>WY241</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>0320</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>WY281</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>0400</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>ET625</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Ethiopian Airlines</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>0425</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>0450</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>EK867</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Emirates</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>0440</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>PC831</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Pegasus Airlines</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Pendik, Istanbul</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Pendik, Istanbul</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>0445</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>QR1149</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Qatar Airways</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>0530</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Gate Closed</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>OV287</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>0715</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>OV5023</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>0810</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>OV5021</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Fahud</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Fahud</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>0820</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>WY317</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>0825</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>WY223</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>0825</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>OV133</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Duqm</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Duqm</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>0830</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>OV101</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>0830</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>OV811</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Vienna</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Vienna</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>0835</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>OV283</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>0840</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>WY815</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>0840</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>WY603</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>0840</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>WY903</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>0845</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>WY823</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>0845</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>OV241</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>0850</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>6Q782</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>6Q</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Damascus</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Damascus</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>0900</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>FZ046</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>flydubai</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>0910</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>WY203</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>0920</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>OV335</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Baghdad</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Baghdad</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>0940</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>OV271</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>0940</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>G9113</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Air Arabia</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>OV365</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>WY831</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>WY245</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>EY693</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Etihad Airways</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>OV927</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Almaty</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Almaty</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>1220</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Delayed</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>OV103</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>OV205</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>WY413</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Amman</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Amman</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>WY117</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>1320</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>OV5025</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>1330</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>OV285</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>WY683</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>1355</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>WY101</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>1415</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>OV227</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Kuwait City</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Kuwait City</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>OV391</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Port Sudan</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Port Sudan</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>WY609</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>WY663</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>1435</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>WY405</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>1440</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>WY655</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Manama</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Manama</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>1445</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>WY675</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>1450</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>WY143</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Ferno</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Ferno</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>1505</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>WY291</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>PF737</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Sialkot</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Sialkot</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>1515</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>OV403</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>1530</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>WY907</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>1530</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>OV213</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Ad Dammam</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Ad Dammam</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>1630</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>OV245</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>1720</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>OV105</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>1730</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>WY669</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>1805</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>WY681</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>1850</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>WY635</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>1850</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>WY647</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Kuwait City</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Kuwait City</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>1855</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>OV107</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>1930</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>WY921</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>1940</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>G9119</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Air Arabia</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>1950</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>WY695</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Ad Dammam</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Ad Dammam</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>IX712</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Kannur</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Kannur</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>WY661</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>WY611</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>FZ048</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>flydubai</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2045</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>IX164</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>2115</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>WY407</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>WY817</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>2145</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>WY673</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>2145</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>OV497</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>2215</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>OV773</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>2230</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>QR1125</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Qatar Airways</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>OV597</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Peshawar</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Peshawar</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>IX236</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>0015</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>OV761</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>28SEP</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>0025</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>2026-09-28 01:36</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/flight_data/live_flights.xlsx
+++ b/flight_data/live_flights.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -512,6 +512,57 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>IX236</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0015</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2026-09-29 01:15</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-09-29 01:15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/flight_data/live_flights.xlsx
+++ b/flight_data/live_flights.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -515,7 +515,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IX236</t>
+          <t>OV5031</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,22 +525,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Fahud</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Fahud</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0015</t>
+          <t>0800</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -554,12 +554,4932 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-09-29 01:15</t>
+          <t>2026-09-29 07:00</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-09-29 01:15</t>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>WY317</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0825</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>OV101</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0830</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>WY815</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0840</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>WY603</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0840</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Last Call</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>OV283</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0840</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>WY903</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0845</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>WY823</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0845</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>OV371</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Kigali</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Kigali</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0900</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FZ046</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>flydubai</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0910</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>WY843</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Manila</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Manila</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0915</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>WY203</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0920</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>WY831</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0935</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>OV335</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Baghdad</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Baghdad</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0940</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>OV211</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Ad Dammam</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Ad Dammam</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0945</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>G9113</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Air Arabia</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>OV241</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>WY245</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>WY689</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1055</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>IA642</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Baghdad</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Baghdad</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1115</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Last Call</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>OV5093</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Mukhaizna Oil Field</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Mukhaizna Oil Field</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Gate Open</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EY693</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Etihad Airways</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>OV205</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>WY171</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1310</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>OV103</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>1315</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>WY909</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1320</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>WY699</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Taif</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Taif</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1335</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>OV285</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>OV273</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1345</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>WY683</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1355</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>WY123</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1355</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>OV135</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Duqm</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Duqm</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>OV293</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Abha</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Abha</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1410</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BG722</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Biman Bangladesh Airlines</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1410</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>WY101</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1415</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>OV227</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Kuwait City</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Kuwait City</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>WY693</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Ad Dammam</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Ad Dammam</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>WY663</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1435</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PK230</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>PIA Pakistan International Airlines</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Lahore</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Lahore</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1435</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>WY405</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1440</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>OV315</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Al Jiza</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Al Jiza</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1450</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>WY675</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1450</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PF733</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Lahore</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Lahore</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>WY291</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1515</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>OV403</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1530</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>WY183</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1555</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>OV105</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1730</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Delayed</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>OV901</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Beringin</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Beringin</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1735</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>WY623</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1745</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>WY647</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Kuwait City</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Kuwait City</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1855</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>OV107</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1930</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>WY921</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1940</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>G9119</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Air Arabia</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1950</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>WY681</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>WY611</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>FZ048</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>flydubai</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2045</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>IX164</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2115</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>WY821</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2120</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>MS931</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Egyptair</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2125</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>WY817</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2150</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>WY661</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2155</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>OV437</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Colombo</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Colombo</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2215</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>OV773</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2230</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>OV735</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2230</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>OV563</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Rawalpindi</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Rawalpindi</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>OV521</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Lahore</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Lahore</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>QR1125</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Qatar Airways</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>WY673</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2305</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>OV705</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2320</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>IX550</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2325</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>EY697</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Etihad Airways</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2350</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>OV537</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Multan</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Multan</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2355</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>OV497</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2355</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6E1268</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2355</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>GF567</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Gulf Air</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Manama</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Manama</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2355</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>IX236</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>0015</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>OV761</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>0025</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>OV421</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Sylhet</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Sylhet</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>0045</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>0106</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>OV401</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>0115</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>TK775</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Turkish Airlines</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>0130</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>WY685</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>0145</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>WY849</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>0150</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>WY251</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>0205</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>BS322</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>0200</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>0216</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>IX892</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Mangaluru</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Mangaluru</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>0215</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>WY225</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>WY211</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>6E1274</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>IX442</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>WY265</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>0300</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>6E1272</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>0300</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>OV513</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>0315</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>0341</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>WY241</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>0320</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>ET625</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ethiopian Airlines</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>0425</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>EK867</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Emirates</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>0440</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>0457</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>J4611</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>J4</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Port Sudan</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Port Sudan</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>0430</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>0522</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>QR1149</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>29SEP</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Qatar Airways</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>0530</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:00</t>
         </is>
       </c>
     </row>

--- a/flight_data/live_flights.xlsx
+++ b/flight_data/live_flights.xlsx
@@ -515,7 +515,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>OV5031</t>
+          <t>WY171</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,22 +525,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Fahud</t>
+          <t>Amsterdam</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fahud</t>
+          <t>Amsterdam</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0800</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -554,19 +554,19 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WY317</t>
+          <t>OV103</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -576,22 +576,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0825</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -605,19 +605,19 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>OV101</t>
+          <t>WY909</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -627,7 +627,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0830</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -656,19 +656,19 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WY815</t>
+          <t>WY699</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -683,17 +683,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Taif</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Taif</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0840</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -707,19 +707,19 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WY603</t>
+          <t>OV285</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -729,28 +729,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DXB</t>
+          <t>JED</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Jeddah</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0840</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1410</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Last Call</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -758,19 +762,19 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OV283</t>
+          <t>OV273</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -785,20 +789,24 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>JED</t>
+          <t>Medina</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeddah</t>
+          <t>Medina</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0840</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>1345</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1407</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Departed</t>
@@ -809,19 +817,19 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WY903</t>
+          <t>WY683</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -836,17 +844,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Riyadh</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Riyadh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0845</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -860,19 +868,19 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WY823</t>
+          <t>WY123</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -887,17 +895,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sepang</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sepang</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0845</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -911,19 +919,19 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>OV371</t>
+          <t>OV135</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -938,20 +946,24 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Kigali</t>
+          <t>Duqm</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kigali</t>
+          <t>Duqm</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0900</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1417</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Departed</t>
@@ -962,19 +974,19 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FZ046</t>
+          <t>OV293</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -984,22 +996,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>flydubai</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DXB</t>
+          <t>Abha</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Abha</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0910</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1013,19 +1025,19 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WY843</t>
+          <t>BG722</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1035,25 +1047,29 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Biman Bangladesh Airlines</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Manila</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Manila</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0915</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>1410</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1427</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Departed</t>
@@ -1064,19 +1080,19 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WY203</t>
+          <t>WY101</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1091,17 +1107,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>LHR</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>London</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0920</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1115,19 +1131,19 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WY831</t>
+          <t>WY693</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1142,17 +1158,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Phuket</t>
+          <t>Ad Dammam</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Phuket</t>
+          <t>Ad Dammam</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0935</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1166,19 +1182,19 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OV335</t>
+          <t>OV227</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1193,20 +1209,24 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Baghdad</t>
+          <t>Kuwait City</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Baghdad</t>
+          <t>Kuwait City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0940</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1457</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Departed</t>
@@ -1217,19 +1237,19 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>OV211</t>
+          <t>WY663</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1239,22 +1259,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ad Dammam</t>
+          <t>DOH</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ad Dammam</t>
+          <t>Doha</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0945</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -1268,19 +1288,19 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G9113</t>
+          <t>PK230</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1290,25 +1310,29 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Air Arabia</t>
+          <t>PIA Pakistan International Airlines</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sharjah</t>
+          <t>Lahore</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sharjah</t>
+          <t>Lahore</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>1435</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1452</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Departed</t>
@@ -1319,19 +1343,19 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>OV241</t>
+          <t>WY405</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1341,22 +1365,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sharjah</t>
+          <t>Cairo</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sharjah</t>
+          <t>Cairo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1370,19 +1394,19 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>WY245</t>
+          <t>WY675</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1397,17 +1421,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>JED</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>Jeddah</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -1421,19 +1445,19 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>WY689</t>
+          <t>OV315</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1443,22 +1467,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>JED</t>
+          <t>Al Jiza</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jeddah</t>
+          <t>Al Jiza</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -1472,19 +1496,19 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IA642</t>
+          <t>PF733</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1494,28 +1518,32 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Baghdad</t>
+          <t>Lahore</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Baghdad</t>
+          <t>Lahore</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1115</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1523</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Last Call</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -1523,19 +1551,19 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>OV5093</t>
+          <t>WY291</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1545,28 +1573,28 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Mukhaizna Oil Field</t>
+          <t>Calicut</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mukhaizna Oil Field</t>
+          <t>Calicut</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1515</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Gate Open</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -1574,19 +1602,19 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EY693</t>
+          <t>OV403</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1596,28 +1624,28 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Etihad Airways</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Abu Dhabi</t>
+          <t>Chattogram</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Abu Dhabi</t>
+          <t>Chattogram</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>1530</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -1625,19 +1653,19 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>OV205</t>
+          <t>WY183</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1647,28 +1675,28 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Riyadh</t>
+          <t>Moscow</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Riyadh</t>
+          <t>Moscow</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>1555</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -1676,19 +1704,19 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>WY171</t>
+          <t>OV105</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1698,28 +1726,32 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1310</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1733</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Boarding</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -1727,19 +1759,19 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>OV103</t>
+          <t>OV901</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1754,23 +1786,23 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Beringin</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Beringin</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Gate Closed</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -1778,19 +1810,19 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>WY909</t>
+          <t>WY623</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1805,23 +1837,23 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>DXB</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1745</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Gate Closed</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -1829,19 +1861,19 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>WY699</t>
+          <t>WY647</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1856,17 +1888,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Taif</t>
+          <t>Kuwait City</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Taif</t>
+          <t>Kuwait City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -1880,19 +1912,19 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>OV285</t>
+          <t>OV107</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1907,17 +1939,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>JED</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Jeddah</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1930</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -1931,19 +1963,19 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>OV273</t>
+          <t>WY921</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1953,22 +1985,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Medina</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Medina</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -1982,19 +2014,19 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>WY683</t>
+          <t>G9119</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2004,28 +2036,28 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Air Arabia</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Riyadh</t>
+          <t>Sharjah</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Riyadh</t>
+          <t>Sharjah</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Gate Changed</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -2033,19 +2065,19 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>WY123</t>
+          <t>WY681</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2060,17 +2092,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Riyadh</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Riyadh</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -2084,19 +2116,19 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>OV135</t>
+          <t>WY611</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2106,22 +2138,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Duqm</t>
+          <t>DXB</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Duqm</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -2135,19 +2167,19 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>OV293</t>
+          <t>FZ048</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2157,22 +2189,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>flydubai</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Abha</t>
+          <t>DXB</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Abha</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -2186,19 +2218,19 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BG722</t>
+          <t>IX164</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2208,22 +2240,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Biman Bangladesh Airlines</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>2115</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -2237,19 +2269,19 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>WY101</t>
+          <t>WY821</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2264,17 +2296,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LHR</t>
+          <t>Sepang</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Sepang</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t>2120</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -2288,19 +2320,19 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>OV227</t>
+          <t>MS931</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2310,22 +2342,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Egyptair</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Kuwait City</t>
+          <t>Cairo</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kuwait City</t>
+          <t>Cairo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -2339,19 +2371,19 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>WY693</t>
+          <t>WY817</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2366,17 +2398,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ad Dammam</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ad Dammam</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -2390,19 +2422,19 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>WY663</t>
+          <t>WY661</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2427,7 +2459,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>2155</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -2441,19 +2473,19 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PK230</t>
+          <t>OV437</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2463,22 +2495,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PIA Pakistan International Airlines</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Lahore</t>
+          <t>Colombo</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lahore</t>
+          <t>Colombo</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -2492,19 +2524,19 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>WY405</t>
+          <t>OV773</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2514,22 +2546,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Cairo</t>
+          <t>Calicut</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cairo</t>
+          <t>Calicut</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>2230</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -2543,19 +2575,19 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>OV315</t>
+          <t>OV735</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2570,17 +2602,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Al Jiza</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Jiza</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>2230</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -2594,19 +2626,19 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>WY675</t>
+          <t>QR1125</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2616,22 +2648,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Qatar Airways</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>JED</t>
+          <t>DOH</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Jeddah</t>
+          <t>Doha</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -2645,19 +2677,19 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PF733</t>
+          <t>OV563</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2667,22 +2699,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Lahore</t>
+          <t>Rawalpindi</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lahore</t>
+          <t>Rawalpindi</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -2696,19 +2728,19 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>WY291</t>
+          <t>OV521</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2718,22 +2750,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Calicut</t>
+          <t>Lahore</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Calicut</t>
+          <t>Lahore</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1515</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -2747,19 +2779,19 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>OV403</t>
+          <t>WY673</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2769,22 +2801,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Chattogram</t>
+          <t>JED</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Chattogram</t>
+          <t>Jeddah</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1530</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -2798,19 +2830,19 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>WY183</t>
+          <t>OV705</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2820,22 +2852,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Moscow</t>
+          <t>Lucknow</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Moscow</t>
+          <t>Lucknow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1555</t>
+          <t>2320</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -2849,19 +2881,19 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>OV105</t>
+          <t>IX550</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2871,32 +2903,28 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Thiruvananthapuram</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Thiruvananthapuram</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>1730</t>
-        </is>
-      </c>
+          <t>2325</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -2904,19 +2932,19 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>OV901</t>
+          <t>EY697</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2926,22 +2954,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Etihad Airways</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Beringin</t>
+          <t>Abu Dhabi</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Beringin</t>
+          <t>Abu Dhabi</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -2955,19 +2983,19 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>WY623</t>
+          <t>6E1268</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2977,22 +3005,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>6E</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>DXB</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1745</t>
+          <t>2355</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -3006,19 +3034,19 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>WY647</t>
+          <t>OV537</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3028,22 +3056,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Kuwait City</t>
+          <t>Multan</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kuwait City</t>
+          <t>Multan</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>2355</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -3057,19 +3085,19 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>OV107</t>
+          <t>OV497</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3084,17 +3112,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>2355</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -3108,19 +3136,19 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>WY921</t>
+          <t>GF567</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3130,22 +3158,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Gulf Air</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Manama</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Manama</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>2355</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -3159,19 +3187,19 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>G9119</t>
+          <t>IX236</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3181,28 +3209,28 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Air Arabia</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Sharjah</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sharjah</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>0015</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -3210,19 +3238,19 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>WY681</t>
+          <t>OV761</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3232,28 +3260,28 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Riyadh</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Riyadh</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>0025</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -3261,19 +3289,19 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>WY611</t>
+          <t>OV421</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3283,28 +3311,32 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>DXB</t>
+          <t>Sylhet</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Sylhet</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
+          <t>0045</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>0106</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -3312,19 +3344,19 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FZ048</t>
+          <t>OV401</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3334,28 +3366,28 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>flydubai</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>DXB</t>
+          <t>Chattogram</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Chattogram</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>0115</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -3363,19 +3395,19 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>IX164</t>
+          <t>TK775</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3385,28 +3417,28 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Turkish Airlines</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2115</t>
+          <t>0130</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -3414,19 +3446,19 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>WY821</t>
+          <t>WY685</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3441,23 +3473,23 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Sepang</t>
+          <t>Riyadh</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sepang</t>
+          <t>Riyadh</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>0145</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -3465,19 +3497,19 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MS931</t>
+          <t>WY849</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3487,28 +3519,28 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Egyptair</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Cairo</t>
+          <t>Jakarta</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Cairo</t>
+          <t>Jakarta</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>0150</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -3516,19 +3548,19 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>WY817</t>
+          <t>WY251</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3543,23 +3575,23 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>0205</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -3567,19 +3599,19 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>WY661</t>
+          <t>BS322</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3589,28 +3621,32 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>BS</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>DOH</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Doha</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2155</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
+          <t>0200</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>0216</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -3618,19 +3654,19 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>OV437</t>
+          <t>IX892</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3640,28 +3676,28 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Colombo</t>
+          <t>Mangaluru</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Colombo</t>
+          <t>Mangaluru</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2215</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -3669,19 +3705,19 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>OV773</t>
+          <t>WY225</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3691,28 +3727,28 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Calicut</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Calicut</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -3720,19 +3756,19 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>OV735</t>
+          <t>WY211</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3742,28 +3778,28 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Thiruvananthapuram</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Thiruvananthapuram</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -3771,19 +3807,19 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>OV563</t>
+          <t>6E1274</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3793,28 +3829,28 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>6E</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Rawalpindi</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rawalpindi</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>0250</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -3822,19 +3858,19 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>OV521</t>
+          <t>IX442</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3844,28 +3880,28 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Lahore</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Lahore</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>0250</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -3873,19 +3909,19 @@
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>QR1125</t>
+          <t>WY265</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3895,28 +3931,28 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Qatar Airways</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>DOH</t>
+          <t>Lucknow</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Doha</t>
+          <t>Lucknow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>0300</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -3924,19 +3960,19 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>WY673</t>
+          <t>6E1272</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3946,28 +3982,28 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>6E</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>JED</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Jeddah</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>0300</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -3975,19 +4011,19 @@
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>OV705</t>
+          <t>OV513</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4002,23 +4038,27 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Lucknow</t>
+          <t>Karachi</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Lucknow</t>
+          <t>Karachi</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2320</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr"/>
+          <t>0315</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>0341</t>
+        </is>
+      </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -4026,19 +4066,19 @@
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>IX550</t>
+          <t>WY241</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4048,28 +4088,28 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Thiruvananthapuram</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Thiruvananthapuram</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2325</t>
+          <t>0320</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -4077,19 +4117,19 @@
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>EY697</t>
+          <t>ET625</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4099,28 +4139,28 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Etihad Airways</t>
+          <t>Ethiopian Airlines</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Abu Dhabi</t>
+          <t>Addis Ababa</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Abu Dhabi</t>
+          <t>Addis Ababa</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2350</t>
+          <t>0425</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -4128,19 +4168,19 @@
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>OV537</t>
+          <t>EK867</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4150,28 +4190,32 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Emirates</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Multan</t>
+          <t>DXB</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Multan</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2355</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr"/>
+          <t>0440</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>0457</t>
+        </is>
+      </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -4179,19 +4223,19 @@
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>OV497</t>
+          <t>J4611</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4201,28 +4245,32 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>J4</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Port Sudan</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Port Sudan</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2355</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr"/>
+          <t>0430</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>0522</t>
+        </is>
+      </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -4230,19 +4278,19 @@
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>6E1268</t>
+          <t>QR1149</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4252,28 +4300,28 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>6E</t>
+          <t>Qatar Airways</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>DOH</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Doha</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2355</t>
+          <t>0530</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -4281,19 +4329,19 @@
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>GF567</t>
+          <t>OV5031</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4303,28 +4351,28 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Gulf Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Manama</t>
+          <t>Fahud</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Manama</t>
+          <t>Fahud</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2355</t>
+          <t>0800</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Departed</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -4332,19 +4380,19 @@
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>IX236</t>
+          <t>WY317</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4354,22 +4402,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>0015</t>
+          <t>0825</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -4383,19 +4431,19 @@
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>OV761</t>
+          <t>OV101</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4410,17 +4458,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>0025</t>
+          <t>0830</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
@@ -4434,19 +4482,19 @@
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>OV421</t>
+          <t>WY815</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4456,29 +4504,25 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Sylhet</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sylhet</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>0045</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>0106</t>
-        </is>
-      </c>
+          <t>0840</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
           <t>Departed</t>
@@ -4489,19 +4533,19 @@
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>OV401</t>
+          <t>WY603</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4511,28 +4555,28 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Chattogram</t>
+          <t>DXB</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Chattogram</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>0115</t>
+          <t>0840</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Departed</t>
+          <t>Last Call</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -4540,19 +4584,19 @@
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>TK775</t>
+          <t>OV283</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4562,22 +4606,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Turkish Airlines</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>JED</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Jeddah</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>0130</t>
+          <t>0840</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
@@ -4591,19 +4635,19 @@
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>WY685</t>
+          <t>WY903</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4618,17 +4662,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Riyadh</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Riyadh</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>0145</t>
+          <t>0845</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -4642,19 +4686,19 @@
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>WY849</t>
+          <t>WY823</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4669,17 +4713,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Jakarta</t>
+          <t>Sepang</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Jakarta</t>
+          <t>Sepang</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>0150</t>
+          <t>0845</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
@@ -4693,19 +4737,19 @@
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>WY251</t>
+          <t>OV371</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4715,22 +4759,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Kigali</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Kigali</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>0205</t>
+          <t>0900</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
@@ -4744,19 +4788,19 @@
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BS322</t>
+          <t>FZ046</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4766,29 +4810,25 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>BS</t>
+          <t>flydubai</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>DXB</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>0200</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>0216</t>
-        </is>
-      </c>
+          <t>0910</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
           <t>Departed</t>
@@ -4799,19 +4839,19 @@
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>IX892</t>
+          <t>WY843</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4821,22 +4861,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Mangaluru</t>
+          <t>Manila</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Mangaluru</t>
+          <t>Manila</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0915</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
@@ -4850,19 +4890,19 @@
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>WY225</t>
+          <t>WY203</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4877,17 +4917,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0920</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -4901,19 +4941,19 @@
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>WY211</t>
+          <t>WY831</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4928,17 +4968,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Thiruvananthapuram</t>
+          <t>Phuket</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Thiruvananthapuram</t>
+          <t>Phuket</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0935</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -4952,19 +4992,19 @@
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>6E1274</t>
+          <t>OV335</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4974,22 +5014,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>6E</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Baghdad</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Baghdad</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>0250</t>
+          <t>0940</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
@@ -5003,19 +5043,19 @@
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>IX442</t>
+          <t>OV211</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5025,22 +5065,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Ad Dammam</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Ad Dammam</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>0250</t>
+          <t>0945</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -5054,19 +5094,19 @@
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>WY265</t>
+          <t>G9113</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5076,22 +5116,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Air Arabia</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Lucknow</t>
+          <t>Sharjah</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Lucknow</t>
+          <t>Sharjah</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>0300</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
@@ -5105,19 +5145,19 @@
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>6E1272</t>
+          <t>OV241</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5127,22 +5167,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>6E</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Sharjah</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Sharjah</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>0300</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
@@ -5156,19 +5196,19 @@
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>OV513</t>
+          <t>WY245</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5178,29 +5218,25 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Karachi</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Karachi</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>0315</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>0341</t>
-        </is>
-      </c>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
           <t>Departed</t>
@@ -5211,19 +5247,19 @@
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>WY241</t>
+          <t>WY689</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -5238,17 +5274,17 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>JED</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>Jeddah</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>0320</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
@@ -5262,19 +5298,19 @@
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ET625</t>
+          <t>IA642</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5284,22 +5320,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ethiopian Airlines</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Addis Ababa</t>
+          <t>Baghdad</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Addis Ababa</t>
+          <t>Baghdad</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>0425</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
@@ -5313,19 +5349,19 @@
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>EK867</t>
+          <t>OV5093</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -5335,29 +5371,25 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Emirates</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>DXB</t>
+          <t>Mukhaizna Oil Field</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Mukhaizna Oil Field</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>0440</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>0457</t>
-        </is>
-      </c>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
           <t>Departed</t>
@@ -5368,19 +5400,19 @@
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>J4611</t>
+          <t>EY693</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -5390,29 +5422,25 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>J4</t>
+          <t>Etihad Airways</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Port Sudan</t>
+          <t>Abu Dhabi</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Port Sudan</t>
+          <t>Abu Dhabi</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>0430</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>0522</t>
-        </is>
-      </c>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
           <t>Departed</t>
@@ -5423,19 +5451,19 @@
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>QR1149</t>
+          <t>OV205</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -5445,22 +5473,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Qatar Airways</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>DOH</t>
+          <t>Riyadh</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Doha</t>
+          <t>Riyadh</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>0530</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
@@ -5474,12 +5502,12 @@
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2026-09-29 07:00</t>
+          <t>2026-09-29 13:55</t>
         </is>
       </c>
     </row>

--- a/flight_data/live_flights.xlsx
+++ b/flight_data/live_flights.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -512,6 +512,6366 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>6E1273</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0150</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>IX441</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0150</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>6E1271</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0200</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>EK866</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Emirates</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0330</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PC830</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Pegasus Airlines</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Pendik, Istanbul</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Pendik, Istanbul</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0330</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ET624</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ethiopian Airlines</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0335</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>QR1148</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Qatar Airways</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0355</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>WY154</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0455</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Arrived</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>WY678</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0510</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>On Time</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>OV498</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0535</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0519</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>OV564</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Rawalpindi</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Rawalpindi</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0545</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0518</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>WY148</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Rome</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Rome</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0545</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>OV736</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0605</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0542</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>OV774</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0605</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>WY144</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Ferno</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Ferno</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0605</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>On Time</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>OV598</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Peshawar</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Peshawar</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0620</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0600</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>WY132</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0620</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>WY674</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0625</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>On Time</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>OV506</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Sialkot</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sialkot</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0635</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>OV762</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0650</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>WY102</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0700</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>WY184</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0705</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>OV784</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>WY686</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>OV706</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0715</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>On Time</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>OV514</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>0730</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>OV902</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Beringin</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Beringin</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>0730</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>OV438</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Colombo</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Colombo</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>0735</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>6Q781</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>6Q</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Damascus</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Damascus</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>0800</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>FZ045</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>flydubai</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>0810</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>OV796</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Jaipur</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Jaipur</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>0845</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>G9112</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Air Arabia</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>0910</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>WY672</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>0950</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>WY252</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1035</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>WY226</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>EY692</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Etihad Airways</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>WY242</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1045</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>WY212</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1050</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>WY266</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1055</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>OV134</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Duqm</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Duqm</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>WY202</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>WY818</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1150</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>OV402</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>WY282</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>OV242</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1210</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>OV102</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>WY822</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>WY604</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>OV5024</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1225</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>WY834</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1225</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>WY904</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>OV5022</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Fahud</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Fahud</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>PF736</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Sialkot</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Sialkot</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1425</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>OV288</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>WY892</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>WY824</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>WY166</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>WY682</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>0015</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>WY662</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>0015</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>WY832</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>0025</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>TK774</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Turkish Airlines</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>0030</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>OV316</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Al Jiza</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Al Jiza</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>0050</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>0013</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>BS321</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>0100</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>TK775</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Turkish Airlines</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>0130</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>0155</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>WY103</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>0135</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>WY685</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>0145</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>OV795</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Jaipur</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Jaipur</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>0150</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>WY849</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>0150</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>OV401</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>0115</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>0214</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>BS322</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>0200</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>WY251</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>0205</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>WY671</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>WY225</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>WY211</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>6E1274</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>IX442</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>WY265</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>0300</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>6E1272</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>0300</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>OV513</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>0315</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>WY241</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>0320</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>WY281</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>0400</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>ET625</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ethiopian Airlines</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>0425</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>EK867</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Emirates</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>0440</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>0500</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Gate Closed</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>PC831</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Pegasus Airlines</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Pendik, Istanbul</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Pendik, Istanbul</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>0445</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>0500</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Gate Closed</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>WY201</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>0505</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Boarding</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>QR1149</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Qatar Airways</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>0530</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Last Call</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>OV287</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>0715</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>OV5023</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>0810</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>WY815</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>0810</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>OV5021</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Fahud</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Fahud</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>0820</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>WY317</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>0825</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>WY223</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>0825</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>OV133</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Duqm</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Duqm</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>0830</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>OV101</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>0830</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>OV811</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Vienna</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Vienna</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>0835</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>OV283</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>0840</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>WY603</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>0840</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>WY903</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>0845</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>WY823</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>0845</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>OV241</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>0850</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>6Q782</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>6Q</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Damascus</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Damascus</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>0900</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>FZ046</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>flydubai</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>0910</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>WY843</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Manila</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Manila</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>0915</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>OV335</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Baghdad</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Baghdad</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>0940</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>OV271</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>0940</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>G9113</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Air Arabia</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>OV365</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>WY245</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>OV927</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Almaty</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Almaty</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>EY693</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Etihad Airways</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>OV103</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>OV205</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>WY413</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Amman</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Amman</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>WY117</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>1320</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>OV5025</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>1330</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>OV285</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>WY683</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>1355</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>WY123</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>1355</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>WY153</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>WY131</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>1410</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>WY101</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>1415</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>OV597</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Peshawar</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Peshawar</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>IX236</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>0015</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>OV761</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>5OCT</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>0025</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/flight_data/live_flights.xlsx
+++ b/flight_data/live_flights.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -512,6 +512,3738 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>6E1273</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0150</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EK866</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Emirates</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0330</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0314</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>J4610</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>J4</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Port Sudan</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Port Sudan</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0330</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0352</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ET624</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ethiopian Airlines</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0335</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0317</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QR1148</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Qatar Airways</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0355</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>WY118</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0405</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>WY124</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0445</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>WY154</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0455</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>WY674</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0510</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>OV774</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0605</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0543</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>OV564</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Rawalpindi</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Rawalpindi</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0605</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>On Time</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>WY144</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Ferno</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Ferno</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0605</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>On Time</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>WY132</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0620</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>On Time</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>OV506</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Sialkot</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sialkot</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0635</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0619</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>OV762</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0650</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0617</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>OV736</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0700</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0632</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>WY102</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0700</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>WY184</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0705</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>OV784</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>On Time</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>OV706</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0715</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>On Time</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>OV514</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0730</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>WY188</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Tashkent</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Tashkent</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0755</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>WY408</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>On Time</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>FZ045</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>flydubai</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0810</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>OV498</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0835</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0816</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>G9112</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Air Arabia</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>0910</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>IA641</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Baghdad</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Baghdad</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>WY824</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>WY662</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>0015</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TK774</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Turkish Airlines</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>0030</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>WY682</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>0040</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BS321</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>0100</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>IX891</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Mangaluru</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Mangaluru</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>0115</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>IX441</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>0150</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>0135</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>6E1271</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>0200</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>0145</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>OV404</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>0215</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>0103</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BS322</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>0200</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>WY251</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>0205</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>IX892</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Mangaluru</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Mangaluru</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>0215</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>WY225</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>IX442</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>6E1274</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>WY265</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>0300</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>6E1272</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>0300</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>OV513</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>0315</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>0334</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>WY241</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0320</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ET625</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ethiopian Airlines</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0425</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>J4611</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>J4</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Port Sudan</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Port Sudan</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0430</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0456</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>EK867</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Emirates</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0440</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>QR1149</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Qatar Airways</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0530</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>OV391</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Port Sudan</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Port Sudan</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0705</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>OV5031</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Fahud</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Fahud</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>0800</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>WY317</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>0825</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>OV101</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>0830</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>OV283</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>0840</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>WY815</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>0840</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>WY603</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>0840</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>WY903</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>0845</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>OV371</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Kigali</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Kigali</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>0900</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>FZ046</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>flydubai</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>0910</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>WY843</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Manila</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Manila</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>0915</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>WY203</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>0920</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>WY831</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>0935</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>OV211</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Ad Dammam</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Ad Dammam</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>0945</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>OV241</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>G9113</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Air Arabia</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>IX236</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>0015</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>0037</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>OV761</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>0025</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>OV421</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Sylhet</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Sylhet</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>0045</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>OV401</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>0115</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>TK775</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Turkish Airlines</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>0130</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>0149</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>WY849</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>0150</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-10-06 02:15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/flight_data/live_flights.xlsx
+++ b/flight_data/live_flights.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M73"/>
+  <dimension ref="A1:M140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -515,7 +515,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6E1273</t>
+          <t>G9112</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,25 +525,29 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6E</t>
+          <t>Air Arabia</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Sharjah</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Sharjah</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0150</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>0910</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0942</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Bags Delivered</t>
@@ -554,19 +558,19 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EK866</t>
+          <t>IA641</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -576,29 +580,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Emirates</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DXB</t>
+          <t>Baghdad</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Baghdad</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0330</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0314</t>
-        </is>
-      </c>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Bags Delivered</t>
@@ -609,19 +609,19 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J4610</t>
+          <t>WY252</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,29 +631,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>J4</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Port Sudan</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Port Sudan</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0330</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0352</t>
-        </is>
-      </c>
+          <t>1035</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Bags Delivered</t>
@@ -664,19 +660,19 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ET624</t>
+          <t>WY226</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -686,29 +682,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopian Airlines</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Addis Ababa</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Addis Ababa</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0335</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0317</t>
-        </is>
-      </c>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Bags Delivered</t>
@@ -719,19 +711,19 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>QR1148</t>
+          <t>EY692</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -741,22 +733,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Qatar Airways</t>
+          <t>Etihad Airways</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DOH</t>
+          <t>Abu Dhabi</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Doha</t>
+          <t>Abu Dhabi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0355</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -770,19 +762,19 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WY118</t>
+          <t>WY242</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -797,17 +789,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Frankfurt am Main</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Frankfurt am Main</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0405</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -821,19 +813,19 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WY124</t>
+          <t>WY266</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -848,17 +840,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Lucknow</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Lucknow</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0445</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -872,19 +864,19 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WY154</t>
+          <t>OV422</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -894,25 +886,29 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Sylhet</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Sylhet</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0455</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>1120</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1058</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Bags Delivered</t>
@@ -923,19 +919,19 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WY674</t>
+          <t>IX337</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -945,25 +941,29 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>JED</t>
+          <t>Calicut</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jeddah</t>
+          <t>Calicut</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0510</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>1205</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1133</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Bags Delivered</t>
@@ -974,19 +974,19 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>OV774</t>
+          <t>OV402</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1001,27 +1001,23 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Calicut</t>
+          <t>Chattogram</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Calicut</t>
+          <t>Chattogram</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0605</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0543</t>
-        </is>
-      </c>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Expected</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1029,19 +1025,19 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>OV564</t>
+          <t>WY844</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1051,28 +1047,28 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Rawalpindi</t>
+          <t>Manila</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rawalpindi</t>
+          <t>Manila</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0605</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>On Time</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1080,19 +1076,19 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WY144</t>
+          <t>WY818</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1107,23 +1103,23 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ferno</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ferno</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0605</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>On Time</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1131,19 +1127,19 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WY132</t>
+          <t>OV5032</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1153,28 +1149,28 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Fahud</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Fahud</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0620</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>On Time</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1182,19 +1178,19 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OV506</t>
+          <t>OV102</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1209,27 +1205,23 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sialkot</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sialkot</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0635</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0619</t>
-        </is>
-      </c>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Expected</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1237,19 +1229,19 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>OV762</t>
+          <t>WY604</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1259,32 +1251,28 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>DXB</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0650</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0617</t>
-        </is>
-      </c>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Expected</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -1292,19 +1280,19 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>OV736</t>
+          <t>WY904</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1314,32 +1302,28 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0700</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0632</t>
-        </is>
-      </c>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Expected</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -1347,19 +1331,19 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>WY102</t>
+          <t>OV242</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1369,25 +1353,29 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LHR</t>
+          <t>Sharjah</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Sharjah</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0700</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>1320</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1304</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Expected</t>
@@ -1398,19 +1386,19 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>WY184</t>
+          <t>PK229</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1420,28 +1408,28 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>PIA Pakistan International Airlines</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Moscow</t>
+          <t>Lahore</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Moscow</t>
+          <t>Lahore</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0705</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Expected</t>
+          <t>On Time</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -1449,19 +1437,19 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>OV784</t>
+          <t>OV212</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1476,23 +1464,23 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Ad Dammam</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Ad Dammam</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0710</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>On Time</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -1500,19 +1488,19 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OV706</t>
+          <t>OV5094</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1527,23 +1515,23 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Lucknow</t>
+          <t>Mukhaizna Oil Field</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lucknow</t>
+          <t>Mukhaizna Oil Field</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0715</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>On Time</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -1551,19 +1539,19 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>OV514</t>
+          <t>OV392</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1578,17 +1566,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Karachi</t>
+          <t>Port Sudan</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Karachi</t>
+          <t>Port Sudan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0730</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1602,19 +1590,19 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>WY188</t>
+          <t>WY204</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1629,23 +1617,23 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Tashkent</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tashkent</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0755</t>
+          <t>1545</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Expected</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -1653,19 +1641,19 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>WY408</t>
+          <t>OV284</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1675,28 +1663,28 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cairo</t>
+          <t>JED</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cairo</t>
+          <t>Jeddah</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0805</t>
+          <t>1620</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>On Time</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -1704,19 +1692,19 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FZ045</t>
+          <t>OV136</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1726,22 +1714,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>flydubai</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>DXB</t>
+          <t>Duqm</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Duqm</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0810</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1755,19 +1743,19 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>OV498</t>
+          <t>OV104</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1782,27 +1770,23 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0835</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>0816</t>
-        </is>
-      </c>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Expected</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -1810,19 +1794,19 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>G9112</t>
+          <t>WY246</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1832,22 +1816,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Air Arabia</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sharjah</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sharjah</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0910</t>
+          <t>1750</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -1861,19 +1845,19 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IA641</t>
+          <t>OV206</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1883,22 +1867,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Baghdad</t>
+          <t>Riyadh</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Baghdad</t>
+          <t>Riyadh</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -1912,19 +1896,19 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>WY824</t>
+          <t>WY690</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1939,23 +1923,23 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sepang</t>
+          <t>JED</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sepang</t>
+          <t>Jeddah</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Bags Delivered</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -1963,19 +1947,19 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>WY662</t>
+          <t>WY664</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2000,13 +1984,13 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0015</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Bags Delivered</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -2014,19 +1998,19 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TK774</t>
+          <t>WY694</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2036,28 +2020,28 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkish Airlines</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Ad Dammam</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Ad Dammam</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0030</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Bags Delivered</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -2065,19 +2049,19 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>WY682</t>
+          <t>WY318</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2092,23 +2076,23 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Riyadh</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Riyadh</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0040</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Bags Delivered</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -2116,19 +2100,19 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BS321</t>
+          <t>G9118</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2138,28 +2122,28 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BS</t>
+          <t>Air Arabia</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Sharjah</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Sharjah</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0100</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Bags Delivered</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -2167,19 +2151,19 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>IX891</t>
+          <t>WY850</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2189,28 +2173,28 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Mangaluru</t>
+          <t>Jakarta</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mangaluru</t>
+          <t>Jakarta</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0115</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Bags Delivered</t>
+          <t>Expected</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -2218,19 +2202,19 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>IX441</t>
+          <t>WY684</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2240,32 +2224,28 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Riyadh</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Riyadh</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0150</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>0135</t>
-        </is>
-      </c>
+          <t>1920</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Bags Delivered</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -2273,19 +2253,19 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6E1271</t>
+          <t>WY824</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2295,29 +2275,25 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>6E</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Sepang</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Sepang</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0200</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>0145</t>
-        </is>
-      </c>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>Bags Delivered</t>
@@ -2328,19 +2304,19 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>OV404</t>
+          <t>WY662</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2350,29 +2326,25 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Chattogram</t>
+          <t>DOH</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Chattogram</t>
+          <t>Doha</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0215</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>0103</t>
-        </is>
-      </c>
+          <t>0015</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>Bags Delivered</t>
@@ -2383,19 +2355,19 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-10-06 02:14</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BS322</t>
+          <t>TK774</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2405,28 +2377,28 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BS</t>
+          <t>Turkish Airlines</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0200</t>
+          <t>0030</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Departed</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -2434,19 +2406,19 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>WY251</t>
+          <t>WY682</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2461,23 +2433,23 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Riyadh</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Riyadh</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0205</t>
+          <t>0040</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Departed</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -2485,19 +2457,19 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>IX892</t>
+          <t>BS321</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2507,28 +2479,28 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>BS</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Mangaluru</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Mangaluru</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0100</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Departed</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -2536,19 +2508,19 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>WY225</t>
+          <t>IX891</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2558,28 +2530,28 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Mangaluru</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Mangaluru</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0115</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Departed</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -2587,19 +2559,19 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>IX442</t>
+          <t>IX441</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2624,13 +2596,17 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0250</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+          <t>0150</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>0135</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Departed</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -2638,19 +2614,19 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6E1274</t>
+          <t>6E1271</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2665,23 +2641,27 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0250</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
+          <t>0200</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>0144</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Departed</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -2689,19 +2669,19 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>WY265</t>
+          <t>OV404</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2711,28 +2691,32 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Lucknow</t>
+          <t>Chattogram</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lucknow</t>
+          <t>Chattogram</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0300</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
+          <t>0215</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>0103</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Departed</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -2740,19 +2724,19 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>6E1272</t>
+          <t>6E1273</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2767,23 +2751,23 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0300</t>
+          <t>0150</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Departed</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -2791,19 +2775,19 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>OV513</t>
+          <t>EK866</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2813,32 +2797,32 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Emirates</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Karachi</t>
+          <t>DXB</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Karachi</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0315</t>
+          <t>0330</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0334</t>
+          <t>0314</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Departed</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -2846,19 +2830,19 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>WY241</t>
+          <t>J4610</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2868,28 +2852,32 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>J4</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>Port Sudan</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>Port Sudan</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0320</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
+          <t>0330</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0352</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Departed</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -2897,19 +2885,19 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ET625</t>
+          <t>ET624</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2934,13 +2922,17 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0425</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
+          <t>0335</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0317</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Departed</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -2948,19 +2940,19 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>J4611</t>
+          <t>QR1148</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2970,32 +2962,28 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>J4</t>
+          <t>Qatar Airways</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Port Sudan</t>
+          <t>DOH</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Port Sudan</t>
+          <t>Doha</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0430</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>0456</t>
-        </is>
-      </c>
+          <t>0355</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Departed</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -3003,19 +2991,19 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>EK867</t>
+          <t>WY118</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3025,28 +3013,28 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Emirates</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>DXB</t>
+          <t>Frankfurt am Main</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Frankfurt am Main</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0440</t>
+          <t>0405</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Departed</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -3054,19 +3042,19 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>QR1149</t>
+          <t>WY124</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3076,28 +3064,28 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Qatar Airways</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>DOH</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Doha</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0530</t>
+          <t>0445</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Departed</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -3105,19 +3093,19 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>OV391</t>
+          <t>WY154</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3127,28 +3115,28 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Port Sudan</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Port Sudan</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0705</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -3156,19 +3144,19 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>OV5031</t>
+          <t>WY674</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3178,28 +3166,28 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Fahud</t>
+          <t>JED</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Fahud</t>
+          <t>Jeddah</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0800</t>
+          <t>0510</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -3207,19 +3195,19 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>WY317</t>
+          <t>OV774</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3229,28 +3217,32 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Calicut</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Calicut</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>0825</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
+          <t>0605</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>0543</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -3258,19 +3250,19 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>OV101</t>
+          <t>OV564</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3285,23 +3277,23 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Rawalpindi</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Rawalpindi</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0830</t>
+          <t>0605</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -3309,19 +3301,19 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>OV283</t>
+          <t>WY144</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3331,28 +3323,28 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>JED</t>
+          <t>Ferno</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Jeddah</t>
+          <t>Ferno</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0840</t>
+          <t>0605</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -3360,19 +3352,19 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>WY815</t>
+          <t>WY132</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3387,23 +3379,23 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0840</t>
+          <t>0620</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -3411,19 +3403,19 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>WY603</t>
+          <t>OV506</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3433,28 +3425,28 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>DXB</t>
+          <t>Sialkot</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Sialkot</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>0840</t>
+          <t>0635</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -3462,19 +3454,19 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>WY903</t>
+          <t>OV762</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3484,28 +3476,32 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>0845</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr"/>
+          <t>0650</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>0617</t>
+        </is>
+      </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -3513,19 +3509,19 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>OV371</t>
+          <t>OV736</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3540,23 +3536,27 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Kigali</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kigali</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>0900</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr"/>
+          <t>0700</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>0632</t>
+        </is>
+      </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -3564,19 +3564,19 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FZ046</t>
+          <t>WY102</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3586,28 +3586,28 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>flydubai</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>DXB</t>
+          <t>LHR</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>London</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>0910</t>
+          <t>0700</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -3615,19 +3615,19 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>WY843</t>
+          <t>WY184</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3642,23 +3642,23 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Manila</t>
+          <t>Moscow</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Manila</t>
+          <t>Moscow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>0915</t>
+          <t>0705</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -3666,19 +3666,19 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>WY203</t>
+          <t>OV784</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3688,28 +3688,28 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>0920</t>
+          <t>0710</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -3717,19 +3717,19 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>WY831</t>
+          <t>OV706</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3739,28 +3739,28 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Phuket</t>
+          <t>Lucknow</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Phuket</t>
+          <t>Lucknow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>0935</t>
+          <t>0715</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -3768,19 +3768,19 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>OV211</t>
+          <t>OV514</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3795,23 +3795,23 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Ad Dammam</t>
+          <t>Karachi</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ad Dammam</t>
+          <t>Karachi</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>0945</t>
+          <t>0730</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -3819,19 +3819,19 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>OV241</t>
+          <t>WY188</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3841,28 +3841,28 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Sharjah</t>
+          <t>Tashkent</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sharjah</t>
+          <t>Tashkent</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>0755</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -3870,19 +3870,19 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>G9113</t>
+          <t>WY408</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3892,28 +3892,28 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Air Arabia</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Sharjah</t>
+          <t>Cairo</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sharjah</t>
+          <t>Cairo</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>0805</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -3921,19 +3921,19 @@
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>IX236</t>
+          <t>FZ045</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3943,32 +3943,28 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>flydubai</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>DXB</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>0015</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>0037</t>
-        </is>
-      </c>
+          <t>0810</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Departed</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -3976,19 +3972,19 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>OV761</t>
+          <t>OV498</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4003,23 +3999,27 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>0025</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr"/>
+          <t>0835</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>0814</t>
+        </is>
+      </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Departed</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -4027,19 +4027,19 @@
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>OV421</t>
+          <t>OV371</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4054,17 +4054,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Sylhet</t>
+          <t>Kigali</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sylhet</t>
+          <t>Kigali</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0900</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -4078,19 +4078,19 @@
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>OV401</t>
+          <t>FZ046</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4100,22 +4100,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>flydubai</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Chattogram</t>
+          <t>DXB</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Chattogram</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>0115</t>
+          <t>0910</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -4129,19 +4129,19 @@
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>TK775</t>
+          <t>WY843</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4151,29 +4151,25 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Turkish Airlines</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Manila</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Manila</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>0130</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>0149</t>
-        </is>
-      </c>
+          <t>0915</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>Departed</t>
@@ -4184,19 +4180,19 @@
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>WY849</t>
+          <t>WY203</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4211,17 +4207,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Jakarta</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Jakarta</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>0150</t>
+          <t>0920</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -4235,12 +4231,3449 @@
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2026-10-06 02:15</t>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>WY831</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>0935</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>OV211</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Ad Dammam</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Ad Dammam</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>0945</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>OV241</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>G9113</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Air Arabia</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>WY245</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>WY689</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>1055</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>IA642</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Baghdad</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Baghdad</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>1115</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>OV5093</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Mukhaizna Oil Field</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Mukhaizna Oil Field</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>EY693</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Etihad Airways</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>OV205</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>IX338</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>1305</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>WY165</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Gate Open</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>WY171</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>1310</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Last Call</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>OV103</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>1315</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Last Call</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>WY117</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>1320</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Last Call</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>WY699</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Taif</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Taif</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>1335</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>OV285</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Gate Open</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>OV273</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>1345</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>WY683</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>1355</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>WY123</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>1355</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>OV135</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Duqm</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Duqm</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>OV293</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Abha</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Abha</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>1410</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>WY101</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>1415</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>WY693</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Ad Dammam</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Ad Dammam</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>OV227</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Kuwait City</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Kuwait City</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>WY663</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>1435</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>PK230</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>PIA Pakistan International Airlines</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Lahore</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Lahore</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>1435</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>WY405</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>1440</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>WY675</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>1450</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>OV315</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Al Jiza</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Al Jiza</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>1530</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>WY907</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>1530</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>WY183</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>1555</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>OV105</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>OV245</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>1720</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>OV901</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Beringin</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Beringin</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>1735</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>WY623</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>1745</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>WY669</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>1805</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>WY681</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>1850</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>WY647</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Kuwait City</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Kuwait City</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>1855</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>IX236</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>0015</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>0037</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>OV761</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>0025</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>OV421</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Sylhet</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Sylhet</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>0045</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>OV401</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>0115</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>TK775</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Turkish Airlines</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>0130</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>0149</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>WY849</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>0150</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>BS322</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>0200</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>WY251</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>0205</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>IX892</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Mangaluru</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Mangaluru</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>0215</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>WY225</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>IX442</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>6E1274</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>WY265</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>0300</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>6E1272</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>0300</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>OV513</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>0315</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>0334</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>WY241</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>0320</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>ET625</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Ethiopian Airlines</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>0425</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>J4611</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>J4</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Port Sudan</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Port Sudan</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>0430</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>0456</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>EK867</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Emirates</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>0440</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>QR1149</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Qatar Airways</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>0530</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>OV391</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Port Sudan</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Port Sudan</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>0705</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>OV5031</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Fahud</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Fahud</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>0800</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>WY317</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>0825</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>OV101</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>0830</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>WY815</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>0840</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>WY603</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>0840</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>OV283</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>0840</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>0858</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>WY903</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>6OCT</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>0845</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:04</t>
         </is>
       </c>
     </row>

--- a/flight_data/live_flights.xlsx
+++ b/flight_data/live_flights.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -512,6 +512,7845 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>WY166</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>WY682</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0015</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>WY662</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0015</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TK774</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Turkish Airlines</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0030</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>OV316</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Al Jiza</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Al Jiza</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0035</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0008</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BS321</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0100</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>6E1273</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0150</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Bags Delivered</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>6E1271</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0200</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0219</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Bags on Belt</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TC408</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>TC</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Dar es Salaam</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Dar es Salaam</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0220</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0343</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EK866</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Emirates</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0330</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0315</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PC830</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Pegasus Airlines</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Pendik, Istanbul</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Pendik, Istanbul</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0330</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>On Time</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3T266</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3T</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Khartoum</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Khartoum</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0330</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ET624</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ethiopian Airlines</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0335</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>On Time</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>QR1148</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Qatar Airways</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0355</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>On Time</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>WY412</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Amman</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Amman</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0405</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>WY118</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0405</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>On Time</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>WY124</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0445</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>WY674</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0510</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>WY172</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0515</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>OV522</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Lahore</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Lahore</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0540</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>OV538</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Multan</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Multan</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0545</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>OV774</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0605</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>OV736</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>0605</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>OV762</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0650</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>WY102</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0700</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>WY184</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>0705</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>On Time</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>WY686</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>0710</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>OV706</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>0715</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>OV902</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Beringin</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Beringin</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>0725</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>On Time</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>OV514</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>0730</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>OV438</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Colombo</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Colombo</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>0735</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>FZ045</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>flydubai</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>0810</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>OV796</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Jaipur</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Jaipur</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>0830</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>G9112</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Air Arabia</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>0910</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>WY672</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>0950</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>OV498</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>WY252</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1035</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>WY226</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>EY692</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Etihad Airways</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>WY242</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1045</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>WY298</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1050</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>WY212</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1050</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>WY266</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1055</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>OV5042</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>OV134</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Duqm</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Duqm</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>WY818</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1150</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>OV402</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>WY844</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Manila</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Manila</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>OV242</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1210</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>OV102</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>WY822</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>WY604</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>BG721</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Biman Bangladesh Airlines</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1220</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>WY834</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1225</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>WY202</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>1225</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>WY904</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>PF734</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Rawalpindi</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Rawalpindi</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>1310</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>OV5094</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Mukhaizna Oil Field</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Mukhaizna Oil Field</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>1445</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>OV104</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>OV284</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>1620</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>WY224</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>1640</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>OV272</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>1645</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>OV5044</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>1750</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>WY254</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1750</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>WY610</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>1805</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>WY664</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1840</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>WY318</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>1850</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>MU2051</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>China Eastern</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>1855</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>G9118</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Air Arabia</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1900</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>WY850</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>IX711</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Kannur</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Kannur</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>WY684</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>1920</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>WY908</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>1925</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>WY656</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Manama</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Manama</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>1855</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2140</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>BG722</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Biman Bangladesh Airlines</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>0029</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>IX236</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>0015</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>OV761</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>0025</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>OV401</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>0115</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>TK775</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Turkish Airlines</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>0130</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>OV795</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Jaipur</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Jaipur</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>0135</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>WY685</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>0145</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>WY849</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>0150</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>BS322</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>0200</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>0220</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>WY251</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>0205</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>WY671</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>WY225</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>WY211</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Departed</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>6E1274</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Last Call</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>WY265</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>0300</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Gate Closed</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>6E1272</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>0300</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Boarding</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>WY297</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>0305</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Last Call</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>OV513</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>0315</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Last Call</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>WY241</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>0320</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Boarding</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>TC409</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>TC</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Zanzibar</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Zanzibar</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>0350</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>ET625</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ethiopian Airlines</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>0425</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>3T267</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>3T</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Khartoum</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Khartoum</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>0430</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>PC831</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Pegasus Airlines</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Pendik, Istanbul</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Pendik, Istanbul</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>0435</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>EK867</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Emirates</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>0440</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>QR1149</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Qatar Airways</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>0530</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>WY201</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>0600</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>OV5041</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>0745</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>WY223</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>0825</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>WY317</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>0825</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>OV133</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Duqm</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Duqm</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>0830</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>OV101</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>0830</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>OV811</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Vienna</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Vienna</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>0835</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>OV283</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>0840</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>WY815</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>0840</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>WY603</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>0840</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>WY903</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>0845</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>WY823</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Sepang</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>0845</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>OV241</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>0850</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>FZ046</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>flydubai</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>0910</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>WY843</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Manila</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Manila</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>0915</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>WY705</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Dar es Salaam</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Dar es Salaam</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>0915</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>WY253</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>0920</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>WY2175</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Astana</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Astana</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>0930</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>OV271</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>0940</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>G9113</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Air Arabia</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>OV365</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>WY831</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>1125</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>OV5093</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Mukhaizna Oil Field</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Mukhaizna Oil Field</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>EY693</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Etihad Airways</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>OV103</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>WY413</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Amman</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Amman</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>OV5043</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Marmul</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>1330</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>OV285</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>WY683</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>1355</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>OV337</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Baghdad</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Baghdad</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>PF735</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Rawalpindi</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Rawalpindi</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>WY153</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>BG122</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Biman Bangladesh Airlines</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>1410</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>WY101</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>1415</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>OV391</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Port Sudan</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Port Sudan</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>1420</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>OV227</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Kuwait City</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Kuwait City</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>WY609</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>WY663</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>1435</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>WY405</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>1440</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>WY675</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>1450</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>WY679</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>1505</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>WY147</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Rome</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Rome</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>1505</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>WY143</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Ferno</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Ferno</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>1505</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>WY291</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>OV403</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Chattogram</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>1530</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>WY907</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>1530</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>OV213</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Ad Dammam</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Ad Dammam</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>1630</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>WY655</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Manama</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Manama</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>1445</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>1730</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Delayed</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>OV771</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Calicut</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>WY909</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>WY669</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>DOH</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Doha</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>1805</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>OV105</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Salam Air</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Salalah</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>1850</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>WY635</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>1850</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>WY647</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>7OCT</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Oman Air</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Kuwait City</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Kuwait City</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>1855</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/flight_data/live_flights.xlsx
+++ b/flight_data/live_flights.xlsx
@@ -515,7 +515,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WY166</t>
+          <t>OV774</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,22 +525,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Calicut</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Calicut</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>0605</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -554,19 +554,19 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WY682</t>
+          <t>OV762</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -576,25 +576,29 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Riyadh</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Riyadh</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0015</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>0650</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0618</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Bags Delivered</t>
@@ -605,19 +609,19 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WY662</t>
+          <t>OV706</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -627,25 +631,29 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DOH</t>
+          <t>Lucknow</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Doha</t>
+          <t>Lucknow</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0015</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>0715</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0635</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Bags Delivered</t>
@@ -656,19 +664,19 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TK774</t>
+          <t>WY102</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -678,22 +686,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkish Airlines</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>LHR</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>London</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0030</t>
+          <t>0700</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -707,19 +715,19 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OV316</t>
+          <t>WY184</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -729,29 +737,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Al Jiza</t>
+          <t>Moscow</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Jiza</t>
+          <t>Moscow</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0035</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0008</t>
-        </is>
-      </c>
+          <t>0705</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Bags Delivered</t>
@@ -762,19 +766,19 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BS321</t>
+          <t>WY686</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -784,22 +788,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BS</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Riyadh</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Riyadh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0100</t>
+          <t>0710</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -813,19 +817,19 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6E1273</t>
+          <t>OV902</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -835,22 +839,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>6E</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Beringin</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Beringin</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0150</t>
+          <t>0725</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -864,19 +868,19 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6E1271</t>
+          <t>OV514</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -886,32 +890,28 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>6E</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Karachi</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Karachi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0200</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0219</t>
-        </is>
-      </c>
+          <t>0730</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Bags on Belt</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -919,19 +919,19 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TC408</t>
+          <t>OV438</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -941,32 +941,28 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TC</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Dar es Salaam</t>
+          <t>Colombo</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dar es Salaam</t>
+          <t>Colombo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0220</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0343</t>
-        </is>
-      </c>
+          <t>0735</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Expected</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -974,19 +970,19 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EK866</t>
+          <t>FZ045</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -996,7 +992,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Emirates</t>
+          <t>flydubai</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1011,17 +1007,13 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0330</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0315</t>
-        </is>
-      </c>
+          <t>0810</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Expected</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1029,19 +1021,19 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PC830</t>
+          <t>OV796</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1051,28 +1043,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pegasus Airlines</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Pendik, Istanbul</t>
+          <t>Jaipur</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pendik, Istanbul</t>
+          <t>Jaipur</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0330</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>0830</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0815</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>On Time</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1080,19 +1076,19 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3T266</t>
+          <t>G9112</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1102,32 +1098,32 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3T</t>
+          <t>Air Arabia</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Khartoum</t>
+          <t>Sharjah</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Khartoum</t>
+          <t>Sharjah</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0330</t>
+          <t>0910</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0948</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Expected</t>
+          <t>Bags on Belt</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1135,19 +1131,19 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ET624</t>
+          <t>WY672</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1157,28 +1153,28 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopian Airlines</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Addis Ababa</t>
+          <t>JED</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Addis Ababa</t>
+          <t>Jeddah</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0335</t>
+          <t>0950</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>On Time</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1186,19 +1182,19 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>QR1148</t>
+          <t>OV498</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1208,22 +1204,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Qatar Airways</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>DOH</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Doha</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0355</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1237,19 +1233,19 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WY412</t>
+          <t>WY252</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1264,17 +1260,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Amman</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Amman</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0405</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -1288,19 +1284,19 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>WY118</t>
+          <t>WY226</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1315,17 +1311,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Frankfurt am Main</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Frankfurt am Main</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0405</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -1339,19 +1335,19 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>WY124</t>
+          <t>EY692</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1361,28 +1357,28 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Etihad Airways</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Abu Dhabi</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Abu Dhabi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0445</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Expected</t>
+          <t>On Time</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -1390,19 +1386,19 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>WY674</t>
+          <t>WY242</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1417,17 +1413,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>JED</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jeddah</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0510</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -1441,19 +1437,19 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>WY172</t>
+          <t>WY298</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1468,17 +1464,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>Calicut</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>Calicut</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0515</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -1492,19 +1488,19 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OV522</t>
+          <t>WY212</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1514,28 +1510,28 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Lahore</t>
+          <t>Thiruvananthapuram</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lahore</t>
+          <t>Thiruvananthapuram</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0540</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>On Time</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -1543,19 +1539,19 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>OV538</t>
+          <t>WY266</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1565,28 +1561,28 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Multan</t>
+          <t>Lucknow</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Multan</t>
+          <t>Lucknow</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0545</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>On Time</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -1594,19 +1590,19 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>OV774</t>
+          <t>OV5042</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1621,23 +1617,23 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Calicut</t>
+          <t>Marmul</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Calicut</t>
+          <t>Marmul</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0605</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>On Time</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -1645,19 +1641,19 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>OV736</t>
+          <t>OV134</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1672,23 +1668,27 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Duqm</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Duqm</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0605</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1113</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Expected</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -1696,19 +1696,19 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>OV762</t>
+          <t>WY818</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1718,28 +1718,28 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0650</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>On Time</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -1747,19 +1747,19 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>WY102</t>
+          <t>OV402</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1769,25 +1769,29 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LHR</t>
+          <t>Chattogram</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Chattogram</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0700</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1117</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Expected</t>
@@ -1798,19 +1802,19 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>WY184</t>
+          <t>WY844</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1825,17 +1829,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Moscow</t>
+          <t>Manila</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Moscow</t>
+          <t>Manila</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0705</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -1849,19 +1853,19 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>WY686</t>
+          <t>OV242</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1871,28 +1875,28 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Riyadh</t>
+          <t>Sharjah</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Riyadh</t>
+          <t>Sharjah</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0710</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>On Time</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -1900,19 +1904,19 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>OV706</t>
+          <t>OV102</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1927,23 +1931,23 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Lucknow</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lucknow</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0715</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>On Time</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -1951,19 +1955,19 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>OV902</t>
+          <t>WY822</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1973,22 +1977,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Beringin</t>
+          <t>Sepang</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Beringin</t>
+          <t>Sepang</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0725</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -2002,19 +2006,19 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>OV514</t>
+          <t>WY604</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2024,22 +2028,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Karachi</t>
+          <t>DXB</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Karachi</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0730</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -2053,19 +2057,19 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>OV438</t>
+          <t>BG721</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2075,22 +2079,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Biman Bangladesh Airlines</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Colombo</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Colombo</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0735</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -2104,19 +2108,19 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FZ045</t>
+          <t>WY834</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2126,28 +2130,28 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>flydubai</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DXB</t>
+          <t>Phuket</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Phuket</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0810</t>
+          <t>1225</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Expected</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -2155,19 +2159,19 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>OV796</t>
+          <t>WY202</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2177,28 +2181,28 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Jaipur</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Jaipur</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0830</t>
+          <t>1225</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Expected</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -2206,19 +2210,19 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>G9112</t>
+          <t>WY904</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2228,22 +2232,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Air Arabia</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sharjah</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sharjah</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0910</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -2257,19 +2261,19 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>WY672</t>
+          <t>PF734</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2279,28 +2283,32 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>JED</t>
+          <t>Rawalpindi</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Jeddah</t>
+          <t>Rawalpindi</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0950</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
+          <t>1310</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1411</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Expected</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -2308,19 +2316,19 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>OV498</t>
+          <t>OV5094</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2335,17 +2343,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Mukhaizna Oil Field</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Mukhaizna Oil Field</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -2359,19 +2367,19 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>WY252</t>
+          <t>OV104</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2381,22 +2389,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -2410,19 +2418,19 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>WY226</t>
+          <t>OV284</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2432,22 +2440,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>JED</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Jeddah</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1620</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -2461,19 +2469,19 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>EY692</t>
+          <t>WY224</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2483,22 +2491,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Etihad Airways</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Abu Dhabi</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Abu Dhabi</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -2512,19 +2520,19 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>WY242</t>
+          <t>OV272</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2534,22 +2542,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>Medina</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>Medina</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1645</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -2563,19 +2571,19 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>WY298</t>
+          <t>OV5044</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2585,22 +2593,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Calicut</t>
+          <t>Marmul</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Calicut</t>
+          <t>Marmul</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1750</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -2614,19 +2622,19 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>WY212</t>
+          <t>WY254</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2641,17 +2649,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Thiruvananthapuram</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Thiruvananthapuram</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1750</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -2665,19 +2673,19 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>WY266</t>
+          <t>WY610</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2692,17 +2700,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Lucknow</t>
+          <t>DXB</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lucknow</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -2716,19 +2724,19 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>OV5042</t>
+          <t>WY664</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2738,22 +2746,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Marmul</t>
+          <t>DOH</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Marmul</t>
+          <t>Doha</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -2767,19 +2775,19 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>OV134</t>
+          <t>WY318</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2789,22 +2797,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Duqm</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Duqm</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -2818,19 +2826,19 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>WY818</t>
+          <t>MU2051</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2840,22 +2848,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>China Eastern</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Beijing</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Beijing</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -2869,19 +2877,19 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>OV402</t>
+          <t>G9118</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2891,22 +2899,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Air Arabia</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Chattogram</t>
+          <t>Sharjah</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Chattogram</t>
+          <t>Sharjah</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -2920,19 +2928,19 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>WY844</t>
+          <t>WY850</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2947,17 +2955,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Manila</t>
+          <t>Jakarta</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Manila</t>
+          <t>Jakarta</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -2971,19 +2979,19 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>OV242</t>
+          <t>IX711</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2993,22 +3001,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Sharjah</t>
+          <t>Kannur</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sharjah</t>
+          <t>Kannur</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -3022,19 +3030,19 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>OV102</t>
+          <t>WY684</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3044,22 +3052,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Riyadh</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Riyadh</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -3073,19 +3081,19 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>WY822</t>
+          <t>WY908</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3100,17 +3108,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Sepang</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sepang</t>
+          <t>Salalah</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -3124,19 +3132,19 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>WY604</t>
+          <t>WY656</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3151,20 +3159,24 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>DXB</t>
+          <t>Manama</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Manama</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1215</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
+          <t>1855</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2140</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>Scheduled</t>
@@ -3175,19 +3187,19 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BG721</t>
+          <t>WY166</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3197,28 +3209,28 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Biman Bangladesh Airlines</t>
+          <t>Oman Air</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -3226,19 +3238,19 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>WY834</t>
+          <t>WY682</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3253,23 +3265,23 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Phuket</t>
+          <t>Riyadh</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Phuket</t>
+          <t>Riyadh</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>0015</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -3277,19 +3289,19 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>WY202</t>
+          <t>WY662</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3304,23 +3316,23 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>DOH</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Doha</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>0015</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -3328,19 +3340,19 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>WY904</t>
+          <t>TK774</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3350,28 +3362,28 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Oman Air</t>
+          <t>Turkish Airlines</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Salalah</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>0030</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -3379,19 +3391,19 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PF734</t>
+          <t>OV316</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3401,28 +3413,32 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>PF</t>
+          <t>Salam Air</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Rawalpindi</t>
+          <t>Al Jiza</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rawalpindi</t>
+          <t>Al Jiza</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1310</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr"/>
+          <t>0035</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>0007</t>
+        </is>
+      </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -3430,19 +3446,19 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>OV5094</t>
+          <t>BS321</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3452,28 +3468,28 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Salam Air</t>
+          <t>BS</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Mukhaizna Oil Field</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Mukhaizna Oil Field</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>0100</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Bags Delivered</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -3481,19 +3497,19 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2026-10-07 00:11</t>
+          <t>2026-10-07 06:07</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-        